--- a/Math/Calculus/工作日志.xlsx
+++ b/Math/Calculus/工作日志.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22188" windowHeight="9180" firstSheet="33" activeTab="35"/>
+    <workbookView windowWidth="22188" windowHeight="9180" firstSheet="27" activeTab="32"/>
   </bookViews>
   <sheets>
     <sheet name="20240302" sheetId="1" r:id="rId1"/>
@@ -43,6 +43,7 @@
     <sheet name="20240424" sheetId="34" r:id="rId34"/>
     <sheet name="20240425" sheetId="35" r:id="rId35"/>
     <sheet name="20240426" sheetId="36" r:id="rId36"/>
+    <sheet name="20240427" sheetId="37" r:id="rId37"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -62,7 +63,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="928" uniqueCount="914">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="935" uniqueCount="922">
   <si>
     <t>（反常）定积分的分拆和合并建立在###定积分存在###的基础上</t>
   </si>
@@ -70,10 +71,19 @@
     <t>伽马函数</t>
   </si>
   <si>
-    <t>Γ(t)=###Int(exp(-x)*x^(t-1),x=0..∞)###（定义式）</t>
-  </si>
-  <si>
-    <t>具有性质:Γ(t)=###(t-1)!###（计算式）</t>
+    <t>积分定义的函数：γ(t)=###Int(0,+∞):(x^(t-a))*e^(-x)dx###</t>
+  </si>
+  <si>
+    <t>递推性质：###γ(t+1)=t*γ(t)###</t>
+  </si>
+  <si>
+    <t>阶乘等价：###γ(t+1)=t!###</t>
+  </si>
+  <si>
+    <t>特殊取值：γ(1/2)=###sqrt(π)###</t>
+  </si>
+  <si>
+    <t>收敛性：###t&gt;0则收敛###</t>
   </si>
   <si>
     <t>反常积分在判断敛散性（而非求出结果）可以直接对被积函数的###因子###使用###等价无穷小###</t>
@@ -124,7 +134,7 @@
     <t>已有等式，求等式的值，可以试着###把两个加起来除2###再变形</t>
   </si>
   <si>
-    <t>嵌套分段函数，采用###整体代入###然后求###内函数不等式###的方式分类讨论</t>
+    <t>分段复合分段函数，采用###内函数整体代入###然后列###内函数与外函数定义域分段构造不等式###的方式分类讨论</t>
   </si>
   <si>
     <t>求与x轴所围面积，先求###零点###，然后###按零点做定积分###</t>
@@ -349,7 +359,16 @@
     <t>由于一侧的x就对应到整个微元，因此积分区间###只有从0到x(y)###</t>
   </si>
   <si>
-    <t>具体点偏导数可以先###代###后###求###，比如f'x(0,0)可以先###求f(x,0)###再###对其求x的导数###</t>
+    <t>具体点偏导数可以先###代###后###求###</t>
+  </si>
+  <si>
+    <t>比如f'x(0,0)，可以先###把y=0代入f(x,y)###得###f(x,0)###</t>
+  </si>
+  <si>
+    <t>再###把f(x,0)看成一元函数g(x)对x求导###得到###g'(x)###，</t>
+  </si>
+  <si>
+    <t>最后###把x=0代入g'(x)###得到###g'(0)###，即###f'x(0,0)###</t>
   </si>
   <si>
     <t>如果z能写成z(u,v)，而u和v又能写成u(x)和v(x)，那么dz/dx=###(dz/du)*(du/dx)+(dz/dv)*(dv/dx)###</t>
@@ -2223,19 +2242,19 @@
     <t>分段函数最多有几阶导？</t>
   </si>
   <si>
-    <t>分段分别进行###泰勒展开###，看看###展开到几次项出现不相等的系数###</t>
+    <t>分段分别进行###泰勒展开###，看看###展开的第几次方项###在###分段处###具有###不同的系数###</t>
   </si>
   <si>
     <t>快速结论：f(x)在x0可导</t>
   </si>
   <si>
-    <t>①h(x)在x0###连续但不可导###，则f(x)*h(x)在x0可导↔###f(x0)=0###</t>
+    <t>①h(x)在x0连续但不可导，则f(x)*h(x)在x0可导↔f(x0)=###0###</t>
   </si>
   <si>
     <t>g(x)=|f(x)|</t>
   </si>
   <si>
-    <t>②f(x0)≠0，g(x)在x0处###可导###（说明x0###不是f(x)的分段点###）</t>
+    <t>②f(x0)≠0，g(x)在x0处###可导###（说明f(x0)###不是###|f|的分段点，即x0###不是###g(x)的分段点）</t>
   </si>
   <si>
     <t>f(x0)=0</t>
@@ -2382,21 +2401,6 @@
     <t>总结：除了###积分中值###其它都是###开区间###</t>
   </si>
   <si>
-    <t>积分定义的函数：γ(t)=###Int(0,+∞):(x^(t-a))*e^(-x)dx###</t>
-  </si>
-  <si>
-    <t>递推性质：###γ(t+1)=t*γ(t)###</t>
-  </si>
-  <si>
-    <t>阶乘等价：###γ(t+1)=t!###</t>
-  </si>
-  <si>
-    <t>特殊取值：γ(1/2)=###sqrt(π)###</t>
-  </si>
-  <si>
-    <t>收敛性：###t&gt;0则收敛###</t>
-  </si>
-  <si>
     <t>常见反常积分敛散性</t>
   </si>
   <si>
@@ -2796,7 +2800,7 @@
     <t>U上面一个o是指###去心邻域###</t>
   </si>
   <si>
-    <t>f(x)og(x)是指###函数f和函数g构成的复合函数###</t>
+    <t>f(x) o g(x)是指###函数f和函数g构成的复合函数f(g(x))###，f o g###≠###g o f（等于或不等于）</t>
   </si>
   <si>
     <t>对角矩阵的对角矩阵可以是零矩阵</t>
@@ -2808,18 +2812,18 @@
     <t>A伴=###|A|*A逆###</t>
   </si>
   <si>
+    <t>(k*A)逆=###A逆/k###</t>
+  </si>
+  <si>
+    <t>(k*A)伴=|k*A|*(k*A)逆=</t>
+  </si>
+  <si>
+    <t>|k*A|*A逆/k=###(k^n)*|A|*A逆/k###=###(k^(n-1))*|A|*A逆###=(k^(n-1))*A伴</t>
+  </si>
+  <si>
     <t>(k*A)伴=###(k^(n-1))*A伴###</t>
   </si>
   <si>
-    <t>(k*A)逆)=###A逆/k###</t>
-  </si>
-  <si>
-    <t>(k*A)伴=|k*A|*(k*A)逆=</t>
-  </si>
-  <si>
-    <t>|k*A|*A逆/k=###(k^n)*|A|*A逆/k###=###(k^(n-1))*|A|*A逆###=(k^(n-1))*A伴</t>
-  </si>
-  <si>
     <t>函数嵌套###可以###用等价无穷小，###不能###用非零因子代入</t>
   </si>
   <si>
@@ -3031,6 +3035,27 @@
   </si>
   <si>
     <t>数列极限un-&gt;a，则|un|-&gt;###|a|###</t>
+  </si>
+  <si>
+    <t>水平渐近线和斜渐近线趋一侧无穷时极限存在时###存在一条渐近线###，如果趋两侧无穷极限不同，则###有2条渐近线###</t>
+  </si>
+  <si>
+    <t>如果一侧有斜渐近线就###没有水平渐近线###，有水平渐近线就###没有斜渐近线###</t>
+  </si>
+  <si>
+    <t>求n阶导一般方法参考20240413第15行，如果是求定点的n=k阶导，还有一种做法</t>
+  </si>
+  <si>
+    <t>保留难###求导###且容易###复现###的表达式的###求导符号###，不做###展开变形###，等全部列出后###用复现部分对消###</t>
+  </si>
+  <si>
+    <t>全部列出后，观察因式是否会###在定点处为0###</t>
+  </si>
+  <si>
+    <t>如果会，被因式乘上的待求导表达式###不用计算直接当0###</t>
+  </si>
+  <si>
+    <t>如果不会，则需要对带求导表达式做展开计算</t>
   </si>
 </sst>
 </file>
@@ -4034,7 +4059,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H12"/>
+  <dimension ref="A1:H15"/>
   <sheetFormatPr defaultColWidth="9.66666666666667" defaultRowHeight="14.4" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="16384" width="9.66666666666667" customWidth="1"/>
@@ -4043,15 +4068,15 @@
     <row r="1" s="1" customFormat="1" spans="1:8">
       <c r="A1" s="1">
         <f>SUM(B1:AZ1)</f>
-        <v>4.66666666666667</v>
+        <v>5.66666666666667</v>
       </c>
       <c r="B1" s="1">
-        <f t="shared" ref="B1:H1" si="0">COUNTA(B2:B2047)/COLUMN()</f>
+        <f t="shared" ref="B1:H1" si="0">COUNTA(B2:B2050)/COLUMN()</f>
         <v>3</v>
       </c>
       <c r="C1" s="1">
         <f t="shared" si="0"/>
-        <v>1.66666666666667</v>
+        <v>2.66666666666667</v>
       </c>
       <c r="D1" s="1">
         <f t="shared" si="0"/>
@@ -4083,67 +4108,87 @@
       </c>
       <c r="C2" s="3"/>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:2">
       <c r="A3" s="3"/>
-      <c r="B3" s="3" t="s">
+      <c r="B3" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="3"/>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="3"/>
-      <c r="B4" s="3"/>
-      <c r="C4" s="3" t="s">
+      <c r="B4"/>
+      <c r="C4" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="3"/>
-      <c r="B5" s="3"/>
-      <c r="C5" s="3" t="s">
+      <c r="B5"/>
+      <c r="C5" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="3"/>
-      <c r="B6" s="3" t="s">
+      <c r="B6"/>
+      <c r="C6" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="3"/>
-    </row>
-    <row r="7" s="4" customFormat="1" spans="2:2">
-      <c r="B7" s="4" t="s">
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" s="3"/>
+      <c r="B7"/>
+      <c r="C7" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="8" s="4" customFormat="1" spans="3:3">
-      <c r="C8" s="4" t="s">
+    <row r="8" spans="1:3">
+      <c r="A8" s="3"/>
+      <c r="B8"/>
+      <c r="C8" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="9" s="4" customFormat="1" spans="3:3">
-      <c r="C9" s="4" t="s">
+    <row r="9" spans="1:3">
+      <c r="A9" s="3"/>
+      <c r="B9" s="3" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="10" s="4" customFormat="1" spans="3:3">
-      <c r="C10" s="4" t="s">
+      <c r="C9" s="3"/>
+    </row>
+    <row r="10" s="4" customFormat="1" spans="2:2">
+      <c r="B10" s="4" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="11" spans="1:3">
-      <c r="A11" s="3"/>
-      <c r="B11" s="3" t="s">
+    <row r="11" s="4" customFormat="1" spans="3:3">
+      <c r="C11" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C11" s="3"/>
-    </row>
-    <row r="12" spans="1:3">
-      <c r="A12" s="3"/>
-      <c r="B12" s="3" t="s">
+    </row>
+    <row r="12" s="4" customFormat="1" spans="3:3">
+      <c r="C12" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="C12" s="3"/>
+    </row>
+    <row r="13" s="4" customFormat="1" spans="3:3">
+      <c r="C13" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14" s="3"/>
+      <c r="B14" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C14" s="3"/>
+    </row>
+    <row r="15" spans="1:3">
+      <c r="A15" s="3"/>
+      <c r="B15" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C15" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4155,21 +4200,24 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H28"/>
+  <dimension ref="A1:H31"/>
   <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelCol="7"/>
+  <cols>
+    <col min="1" max="1" width="9.66666666666667"/>
+  </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" spans="1:8">
       <c r="A1" s="1">
         <f>SUM(B1:AZ1)</f>
-        <v>8.3</v>
+        <v>9.3</v>
       </c>
       <c r="B1" s="1">
-        <f t="shared" ref="B1:H1" si="0">COUNTA(B2:B2049)/COLUMN()</f>
+        <f t="shared" ref="B1:H1" si="0">COUNTA(B2:B2052)/COLUMN()</f>
         <v>3</v>
       </c>
       <c r="C1" s="1">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D1" s="1">
         <f t="shared" si="0"/>
@@ -4197,140 +4245,155 @@
         <v>20240320</v>
       </c>
       <c r="B2" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="3" spans="2:2">
-      <c r="B3" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="4" spans="2:2">
-      <c r="B4" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="5" spans="2:2">
-      <c r="B5" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="6" spans="3:3">
-      <c r="C6" t="s">
+    <row r="3" spans="3:3">
+      <c r="C3" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="7" spans="3:3">
-      <c r="C7" t="s">
+    <row r="4" spans="3:3">
+      <c r="C4" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="8" spans="4:4">
-      <c r="D8" t="s">
+    <row r="5" spans="3:3">
+      <c r="C5" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="9" spans="2:2">
-      <c r="B9" t="s">
+    <row r="6" spans="2:2">
+      <c r="B6" t="s">
         <v>102</v>
+      </c>
+    </row>
+    <row r="7" spans="2:2">
+      <c r="B7" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="8" spans="2:2">
+      <c r="B8" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="9" spans="3:3">
+      <c r="C9" t="s">
+        <v>105</v>
       </c>
     </row>
     <row r="10" spans="3:3">
       <c r="C10" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
     </row>
     <row r="11" spans="4:4">
       <c r="D11" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="12" spans="3:3">
-      <c r="C12" s="3" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="13" spans="4:4">
-      <c r="D13" s="6" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="14" spans="5:8">
-      <c r="E14" s="4" t="s">
         <v>107</v>
       </c>
-      <c r="F14" s="6"/>
-      <c r="G14" s="6"/>
-      <c r="H14" s="6"/>
-    </row>
-    <row r="15" spans="5:5">
-      <c r="E15" s="4" t="s">
+    </row>
+    <row r="12" spans="2:2">
+      <c r="B12" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="16" spans="2:2">
-      <c r="B16" t="s">
+    <row r="13" spans="3:3">
+      <c r="C13" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="17" spans="3:3">
-      <c r="C17" t="s">
+    <row r="14" spans="4:4">
+      <c r="D14" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="18" spans="4:4">
-      <c r="D18" t="s">
+    <row r="15" spans="3:3">
+      <c r="C15" s="3" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="19" spans="4:4">
-      <c r="D19" t="s">
+    <row r="16" spans="4:4">
+      <c r="D16" s="6" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="20" spans="5:5">
-      <c r="E20" t="s">
+    <row r="17" spans="5:8">
+      <c r="E17" s="4" t="s">
         <v>113</v>
       </c>
-    </row>
-    <row r="21" spans="5:5">
-      <c r="E21" t="s">
+      <c r="F17" s="6"/>
+      <c r="G17" s="6"/>
+      <c r="H17" s="6"/>
+    </row>
+    <row r="18" spans="5:5">
+      <c r="E18" s="4" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="22" spans="5:5">
-      <c r="E22" t="s">
+    <row r="19" spans="2:2">
+      <c r="B19" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="23" spans="3:3">
-      <c r="C23" t="s">
+    <row r="20" spans="3:3">
+      <c r="C20" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="24" spans="4:4">
-      <c r="D24" t="s">
+    <row r="21" spans="4:4">
+      <c r="D21" t="s">
         <v>117</v>
+      </c>
+    </row>
+    <row r="22" spans="4:4">
+      <c r="D22" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="23" spans="5:5">
+      <c r="E23" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="24" spans="5:5">
+      <c r="E24" t="s">
+        <v>120</v>
       </c>
     </row>
     <row r="25" spans="5:5">
       <c r="E25" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="26" spans="5:5">
-      <c r="E26" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="27" spans="5:5">
-      <c r="E27" t="s">
-        <v>120</v>
+        <v>121</v>
+      </c>
+    </row>
+    <row r="26" spans="3:3">
+      <c r="C26" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="27" spans="4:4">
+      <c r="D27" t="s">
+        <v>123</v>
       </c>
     </row>
     <row r="28" spans="5:5">
       <c r="E28" t="s">
-        <v>121</v>
+        <v>124</v>
+      </c>
+    </row>
+    <row r="29" spans="5:5">
+      <c r="E29" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="30" spans="5:5">
+      <c r="E30" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="31" spans="5:5">
+      <c r="E31" t="s">
+        <v>127</v>
       </c>
     </row>
   </sheetData>
@@ -4384,107 +4447,107 @@
         <v>20240322</v>
       </c>
       <c r="B2" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
     </row>
     <row r="3" spans="3:3">
       <c r="C3" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
     </row>
     <row r="4" spans="3:3">
       <c r="C4" t="s">
-        <v>124</v>
+        <v>130</v>
       </c>
     </row>
     <row r="5" spans="4:4">
       <c r="D5" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
     </row>
     <row r="6" spans="4:4">
       <c r="D6" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
     </row>
     <row r="7" spans="2:2">
       <c r="B7" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
     </row>
     <row r="8" spans="2:2">
       <c r="B8" t="s">
-        <v>128</v>
+        <v>134</v>
       </c>
     </row>
     <row r="9" spans="3:3">
       <c r="C9" t="s">
-        <v>129</v>
+        <v>135</v>
       </c>
     </row>
     <row r="10" spans="3:3">
       <c r="C10" t="s">
-        <v>130</v>
+        <v>136</v>
       </c>
     </row>
     <row r="11" spans="4:4">
       <c r="D11" t="s">
-        <v>131</v>
+        <v>137</v>
       </c>
     </row>
     <row r="12" spans="4:4">
       <c r="D12" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
     </row>
     <row r="13" spans="3:3">
       <c r="C13" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
     </row>
     <row r="14" spans="4:4">
       <c r="D14" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
     </row>
     <row r="15" spans="4:4">
       <c r="D15" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
     </row>
     <row r="16" spans="4:4">
       <c r="D16" t="s">
-        <v>136</v>
+        <v>142</v>
       </c>
     </row>
     <row r="17" spans="4:4">
       <c r="D17" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
     </row>
     <row r="18" spans="2:2">
       <c r="B18" t="s">
-        <v>138</v>
+        <v>144</v>
       </c>
     </row>
     <row r="19" spans="2:2">
       <c r="B19" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
     </row>
     <row r="20" spans="3:3">
       <c r="C20" t="s">
-        <v>140</v>
+        <v>146</v>
       </c>
     </row>
     <row r="21" spans="3:3">
       <c r="C21" t="s">
-        <v>141</v>
+        <v>147</v>
       </c>
     </row>
     <row r="22" spans="4:4">
       <c r="D22" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
     </row>
   </sheetData>
@@ -4538,92 +4601,92 @@
         <v>20240323</v>
       </c>
       <c r="B2" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
     </row>
     <row r="3" spans="2:2">
       <c r="B3" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
     </row>
     <row r="4" spans="2:2">
       <c r="B4" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
     </row>
     <row r="5" spans="2:2">
       <c r="B5" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
     </row>
     <row r="6" spans="3:3">
       <c r="C6" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
     </row>
     <row r="7" spans="4:4">
       <c r="D7" t="s">
-        <v>148</v>
+        <v>154</v>
       </c>
     </row>
     <row r="8" spans="4:4">
       <c r="D8" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
     </row>
     <row r="9" spans="3:3">
       <c r="C9" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
     </row>
     <row r="10" spans="4:4">
       <c r="D10" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
     </row>
     <row r="11" spans="5:5">
       <c r="E11" t="s">
-        <v>152</v>
+        <v>158</v>
       </c>
     </row>
     <row r="12" spans="5:5">
       <c r="E12" t="s">
-        <v>153</v>
+        <v>159</v>
       </c>
     </row>
     <row r="13" spans="5:5">
       <c r="E13" t="s">
-        <v>154</v>
+        <v>160</v>
       </c>
     </row>
     <row r="14" spans="5:5">
       <c r="E14" t="s">
-        <v>155</v>
+        <v>161</v>
       </c>
     </row>
     <row r="15" spans="4:4">
       <c r="D15" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
     </row>
     <row r="16" spans="5:5">
       <c r="E16" t="s">
-        <v>157</v>
+        <v>163</v>
       </c>
     </row>
     <row r="17" spans="5:5">
       <c r="E17" t="s">
-        <v>158</v>
+        <v>164</v>
       </c>
     </row>
     <row r="18" s="5" customFormat="1" spans="5:5">
       <c r="E18" s="5" t="s">
-        <v>159</v>
+        <v>165</v>
       </c>
     </row>
     <row r="19" spans="5:5">
       <c r="E19" t="s">
-        <v>160</v>
+        <v>166</v>
       </c>
     </row>
   </sheetData>
@@ -4680,152 +4743,152 @@
         <v>20240326</v>
       </c>
       <c r="B2" t="s">
-        <v>161</v>
+        <v>167</v>
       </c>
     </row>
     <row r="3" spans="2:2">
       <c r="B3" t="s">
-        <v>162</v>
+        <v>168</v>
       </c>
     </row>
     <row r="4" spans="2:2">
       <c r="B4" t="s">
-        <v>163</v>
+        <v>169</v>
       </c>
     </row>
     <row r="5" spans="2:2">
       <c r="B5" t="s">
-        <v>164</v>
+        <v>170</v>
       </c>
     </row>
     <row r="6" spans="2:2">
       <c r="B6" t="s">
-        <v>165</v>
+        <v>171</v>
       </c>
     </row>
     <row r="7" spans="2:2">
       <c r="B7" t="s">
-        <v>166</v>
+        <v>172</v>
       </c>
     </row>
     <row r="8" spans="2:2">
       <c r="B8" t="s">
-        <v>167</v>
+        <v>173</v>
       </c>
     </row>
     <row r="9" spans="3:3">
       <c r="C9" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
     </row>
     <row r="10" spans="4:4">
       <c r="D10" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
     </row>
     <row r="11" spans="4:4">
       <c r="D11" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
     </row>
     <row r="12" spans="5:5">
       <c r="E12" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
     </row>
     <row r="13" spans="5:5">
       <c r="E13" t="s">
-        <v>172</v>
+        <v>178</v>
       </c>
     </row>
     <row r="14" spans="4:4">
       <c r="D14" t="s">
-        <v>173</v>
+        <v>179</v>
       </c>
     </row>
     <row r="15" spans="5:5">
       <c r="E15" t="s">
-        <v>174</v>
+        <v>180</v>
       </c>
     </row>
     <row r="16" spans="5:5">
       <c r="E16" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
     </row>
     <row r="17" spans="5:5">
       <c r="E17" t="s">
-        <v>176</v>
+        <v>182</v>
       </c>
     </row>
     <row r="18" spans="3:3">
       <c r="C18" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
     </row>
     <row r="19" spans="4:4">
       <c r="D19" t="s">
-        <v>178</v>
+        <v>184</v>
       </c>
     </row>
     <row r="20" spans="4:4">
       <c r="D20" t="s">
-        <v>179</v>
+        <v>185</v>
       </c>
     </row>
     <row r="21" spans="5:5">
       <c r="E21" t="s">
-        <v>180</v>
+        <v>186</v>
       </c>
     </row>
     <row r="22" spans="5:5">
       <c r="E22" t="s">
-        <v>181</v>
+        <v>187</v>
       </c>
     </row>
     <row r="23" spans="4:4">
       <c r="D23" t="s">
-        <v>182</v>
+        <v>188</v>
       </c>
     </row>
     <row r="24" spans="5:5">
       <c r="E24" t="s">
-        <v>183</v>
+        <v>189</v>
       </c>
     </row>
     <row r="25" spans="5:5">
       <c r="E25" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
     </row>
     <row r="26" spans="2:2">
       <c r="B26" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
     </row>
     <row r="27" spans="2:2">
       <c r="B27" t="s">
-        <v>186</v>
+        <v>192</v>
       </c>
     </row>
     <row r="28" spans="3:3">
       <c r="C28" t="s">
-        <v>187</v>
+        <v>193</v>
       </c>
     </row>
     <row r="29" s="6" customFormat="1" spans="2:2">
       <c r="B29" s="6" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
     </row>
     <row r="30" s="6" customFormat="1" spans="3:3">
       <c r="C30" s="6" t="s">
-        <v>189</v>
+        <v>195</v>
       </c>
     </row>
     <row r="31" s="6" customFormat="1" spans="3:3">
       <c r="C31" s="6" t="s">
-        <v>190</v>
+        <v>196</v>
       </c>
     </row>
   </sheetData>
@@ -4879,27 +4942,27 @@
         <v>20240328</v>
       </c>
       <c r="B2" t="s">
-        <v>191</v>
+        <v>197</v>
       </c>
     </row>
     <row r="3" spans="3:3">
       <c r="C3" t="s">
-        <v>192</v>
+        <v>198</v>
       </c>
     </row>
     <row r="4" spans="3:3">
       <c r="C4" t="s">
-        <v>193</v>
+        <v>199</v>
       </c>
     </row>
     <row r="5" spans="3:3">
       <c r="C5" t="s">
-        <v>194</v>
+        <v>200</v>
       </c>
     </row>
     <row r="6" spans="3:3">
       <c r="C6" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
     </row>
   </sheetData>
@@ -4953,47 +5016,47 @@
         <v>20240401</v>
       </c>
       <c r="B2" t="s">
-        <v>196</v>
+        <v>202</v>
       </c>
     </row>
     <row r="3" spans="3:3">
       <c r="C3" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
     </row>
     <row r="4" s="4" customFormat="1" spans="2:2">
       <c r="B4" s="4" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
     </row>
     <row r="5" s="4" customFormat="1" spans="3:3">
       <c r="C5" s="4" t="s">
-        <v>199</v>
+        <v>205</v>
       </c>
     </row>
     <row r="6" s="4" customFormat="1" spans="3:3">
       <c r="C6" s="4" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
     </row>
     <row r="7" s="4" customFormat="1" spans="3:3">
       <c r="C7" s="4" t="s">
-        <v>201</v>
+        <v>207</v>
       </c>
     </row>
     <row r="8" s="4" customFormat="1" spans="3:3">
       <c r="C8" s="4" t="s">
-        <v>202</v>
+        <v>208</v>
       </c>
     </row>
     <row r="9" s="4" customFormat="1" spans="3:3">
       <c r="C9" s="4" t="s">
-        <v>203</v>
+        <v>209</v>
       </c>
     </row>
     <row r="10" s="4" customFormat="1" spans="3:3">
       <c r="C10" s="4" t="s">
-        <v>204</v>
+        <v>210</v>
       </c>
     </row>
   </sheetData>
@@ -5047,52 +5110,52 @@
         <v>20240402</v>
       </c>
       <c r="B2" t="s">
-        <v>205</v>
+        <v>211</v>
       </c>
     </row>
     <row r="3" spans="2:2">
       <c r="B3" t="s">
-        <v>206</v>
+        <v>212</v>
       </c>
     </row>
     <row r="4" ht="16.8" spans="3:3">
       <c r="C4" t="s">
-        <v>207</v>
+        <v>213</v>
       </c>
     </row>
     <row r="5" ht="16.8" spans="3:3">
       <c r="C5" t="s">
-        <v>208</v>
+        <v>214</v>
       </c>
     </row>
     <row r="6" ht="16.8" spans="3:3">
       <c r="C6" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
     </row>
     <row r="7" ht="16.8" spans="3:3">
       <c r="C7" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
     </row>
     <row r="8" spans="2:2">
       <c r="B8" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
     </row>
     <row r="9" spans="3:3">
       <c r="C9" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
     </row>
     <row r="10" spans="3:3">
       <c r="C10" t="s">
-        <v>213</v>
+        <v>219</v>
       </c>
     </row>
     <row r="11" spans="3:3">
       <c r="C11" t="s">
-        <v>214</v>
+        <v>220</v>
       </c>
     </row>
   </sheetData>
@@ -5146,152 +5209,152 @@
         <v>20240405</v>
       </c>
       <c r="B2" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
     </row>
     <row r="3" spans="2:2">
       <c r="B3" t="s">
-        <v>216</v>
+        <v>222</v>
       </c>
     </row>
     <row r="4" spans="2:2">
       <c r="B4" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="5" spans="2:2">
       <c r="B5" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
     </row>
     <row r="6" spans="2:2">
       <c r="B6" t="s">
-        <v>219</v>
+        <v>225</v>
       </c>
     </row>
     <row r="7" spans="2:2">
       <c r="B7" t="s">
-        <v>220</v>
+        <v>226</v>
       </c>
     </row>
     <row r="8" spans="2:2">
       <c r="B8" t="s">
-        <v>221</v>
+        <v>227</v>
       </c>
     </row>
     <row r="9" s="5" customFormat="1" spans="2:2">
       <c r="B9" s="5" t="s">
-        <v>222</v>
+        <v>228</v>
       </c>
     </row>
     <row r="10" s="5" customFormat="1" spans="2:2">
       <c r="B10" s="5" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
     </row>
     <row r="11" s="5" customFormat="1" spans="3:3">
       <c r="C11" s="5" t="s">
-        <v>224</v>
+        <v>230</v>
       </c>
     </row>
     <row r="12" spans="2:2">
       <c r="B12" t="s">
-        <v>225</v>
+        <v>231</v>
       </c>
     </row>
     <row r="13" spans="3:3">
       <c r="C13" t="s">
-        <v>226</v>
+        <v>232</v>
       </c>
     </row>
     <row r="14" spans="3:3">
       <c r="C14" t="s">
-        <v>227</v>
+        <v>233</v>
       </c>
     </row>
     <row r="15" spans="3:3">
       <c r="C15" t="s">
-        <v>228</v>
+        <v>234</v>
       </c>
     </row>
     <row r="16" spans="4:4">
       <c r="D16" t="s">
-        <v>229</v>
+        <v>235</v>
       </c>
     </row>
     <row r="17" spans="4:4">
       <c r="D17" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
     </row>
     <row r="18" spans="4:4">
       <c r="D18" t="s">
-        <v>231</v>
+        <v>237</v>
       </c>
     </row>
     <row r="19" spans="3:3">
       <c r="C19" t="s">
-        <v>232</v>
+        <v>238</v>
       </c>
     </row>
     <row r="20" spans="4:4">
       <c r="D20" t="s">
-        <v>233</v>
+        <v>239</v>
       </c>
     </row>
     <row r="21" spans="4:4">
       <c r="D21" t="s">
-        <v>234</v>
+        <v>240</v>
       </c>
     </row>
     <row r="22" spans="4:4">
       <c r="D22" t="s">
-        <v>235</v>
+        <v>241</v>
       </c>
     </row>
     <row r="23" spans="3:3">
       <c r="C23" t="s">
-        <v>236</v>
+        <v>242</v>
       </c>
     </row>
     <row r="24" spans="2:2">
       <c r="B24" t="s">
-        <v>237</v>
+        <v>243</v>
       </c>
     </row>
     <row r="25" spans="3:3">
       <c r="C25" t="s">
-        <v>238</v>
+        <v>244</v>
       </c>
     </row>
     <row r="26" spans="3:3">
       <c r="C26" t="s">
-        <v>239</v>
+        <v>245</v>
       </c>
     </row>
     <row r="27" spans="2:2">
       <c r="B27" t="s">
-        <v>240</v>
+        <v>246</v>
       </c>
     </row>
     <row r="28" spans="2:2">
       <c r="B28" t="s">
-        <v>241</v>
+        <v>247</v>
       </c>
     </row>
     <row r="29" spans="2:2">
       <c r="B29" t="s">
-        <v>242</v>
+        <v>248</v>
       </c>
     </row>
     <row r="30" spans="3:3">
       <c r="C30" t="s">
-        <v>243</v>
+        <v>249</v>
       </c>
     </row>
     <row r="31" spans="3:3">
       <c r="C31" t="s">
-        <v>244</v>
+        <v>250</v>
       </c>
     </row>
   </sheetData>
@@ -5345,17 +5408,17 @@
         <v>20240406</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>245</v>
+        <v>251</v>
       </c>
     </row>
     <row r="3" spans="2:2">
       <c r="B3" t="s">
-        <v>246</v>
+        <v>252</v>
       </c>
     </row>
     <row r="4" s="4" customFormat="1" spans="2:2">
       <c r="B4" s="4" t="s">
-        <v>247</v>
+        <v>253</v>
       </c>
     </row>
   </sheetData>
@@ -5409,47 +5472,47 @@
         <v>20240408</v>
       </c>
       <c r="B2" t="s">
-        <v>248</v>
+        <v>254</v>
       </c>
     </row>
     <row r="3" spans="3:3">
       <c r="C3" t="s">
-        <v>249</v>
+        <v>255</v>
       </c>
     </row>
     <row r="4" spans="2:2">
       <c r="B4" t="s">
-        <v>250</v>
+        <v>256</v>
       </c>
     </row>
     <row r="5" spans="2:2">
       <c r="B5" t="s">
-        <v>251</v>
+        <v>257</v>
       </c>
     </row>
     <row r="6" spans="2:2">
       <c r="B6" t="s">
-        <v>252</v>
+        <v>258</v>
       </c>
     </row>
     <row r="7" spans="3:3">
       <c r="C7" t="s">
-        <v>253</v>
+        <v>259</v>
       </c>
     </row>
     <row r="8" spans="3:3">
       <c r="C8" t="s">
-        <v>254</v>
+        <v>260</v>
       </c>
     </row>
     <row r="9" spans="3:3">
       <c r="C9" t="s">
-        <v>255</v>
+        <v>261</v>
       </c>
     </row>
     <row r="10" spans="2:2">
       <c r="B10" t="s">
-        <v>256</v>
+        <v>262</v>
       </c>
     </row>
   </sheetData>
@@ -5506,28 +5569,28 @@
         <v>20240303</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C2" s="3"/>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="3"/>
       <c r="B3" s="3" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C3" s="3"/>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="3"/>
       <c r="B4" s="3" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C4" s="3"/>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="3"/>
       <c r="B5" s="3" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="C5" s="3"/>
     </row>
@@ -5535,34 +5598,34 @@
       <c r="A6" s="3"/>
       <c r="B6" s="3"/>
       <c r="C6" s="3" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="3"/>
       <c r="B7" s="3"/>
       <c r="C7" s="3" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="3"/>
       <c r="B8" s="3"/>
       <c r="C8" s="3" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" s="3"/>
       <c r="B9" s="3" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="C9" s="3"/>
     </row>
     <row r="10" spans="1:3">
       <c r="A10" s="3"/>
       <c r="B10" s="3" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="C10" s="3"/>
     </row>
@@ -5617,107 +5680,107 @@
         <v>20240409</v>
       </c>
       <c r="B2" t="s">
-        <v>257</v>
+        <v>263</v>
       </c>
     </row>
     <row r="3" spans="2:2">
       <c r="B3" t="s">
-        <v>258</v>
+        <v>264</v>
       </c>
     </row>
     <row r="4" spans="3:3">
       <c r="C4" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
     </row>
     <row r="5" spans="4:4">
       <c r="D5" t="s">
-        <v>260</v>
+        <v>266</v>
       </c>
     </row>
     <row r="6" spans="4:4">
       <c r="D6" t="s">
-        <v>261</v>
+        <v>267</v>
       </c>
     </row>
     <row r="7" spans="4:4">
       <c r="D7" t="s">
-        <v>262</v>
+        <v>268</v>
       </c>
     </row>
     <row r="8" spans="3:3">
       <c r="C8" t="s">
-        <v>263</v>
+        <v>269</v>
       </c>
     </row>
     <row r="9" spans="4:4">
       <c r="D9" s="3" t="s">
-        <v>264</v>
+        <v>270</v>
       </c>
     </row>
     <row r="10" spans="4:4">
       <c r="D10" s="3" t="s">
-        <v>265</v>
+        <v>271</v>
       </c>
     </row>
     <row r="11" spans="4:4">
       <c r="D11" s="3" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
     </row>
     <row r="12" spans="4:4">
       <c r="D12" s="3" t="s">
-        <v>267</v>
+        <v>273</v>
       </c>
     </row>
     <row r="13" s="4" customFormat="1" spans="3:3">
       <c r="C13" s="4" t="s">
-        <v>268</v>
+        <v>274</v>
       </c>
     </row>
     <row r="14" s="4" customFormat="1" spans="4:4">
       <c r="D14" s="4" t="s">
-        <v>269</v>
+        <v>275</v>
       </c>
     </row>
     <row r="15" s="4" customFormat="1" spans="4:4">
       <c r="D15" s="4" t="s">
-        <v>270</v>
+        <v>276</v>
       </c>
     </row>
     <row r="16" s="4" customFormat="1" spans="4:4">
       <c r="D16" s="4" t="s">
-        <v>271</v>
+        <v>277</v>
       </c>
     </row>
     <row r="17" s="4" customFormat="1" spans="4:4">
       <c r="D17" s="4" t="s">
-        <v>272</v>
+        <v>278</v>
       </c>
     </row>
     <row r="18" s="4" customFormat="1" spans="4:4">
       <c r="D18" s="4" t="s">
-        <v>273</v>
+        <v>279</v>
       </c>
     </row>
     <row r="19" spans="3:3">
       <c r="C19" t="s">
-        <v>274</v>
+        <v>280</v>
       </c>
     </row>
     <row r="20" spans="4:4">
       <c r="D20" t="s">
-        <v>275</v>
+        <v>281</v>
       </c>
     </row>
     <row r="21" spans="4:4">
       <c r="D21" t="s">
-        <v>276</v>
+        <v>282</v>
       </c>
     </row>
     <row r="22" spans="4:4">
       <c r="D22" t="s">
-        <v>277</v>
+        <v>283</v>
       </c>
     </row>
   </sheetData>
@@ -5771,282 +5834,282 @@
         <v>20240410</v>
       </c>
       <c r="B2" t="s">
-        <v>278</v>
+        <v>284</v>
       </c>
     </row>
     <row r="3" spans="2:2">
       <c r="B3" t="s">
-        <v>279</v>
+        <v>285</v>
       </c>
     </row>
     <row r="4" spans="3:3">
       <c r="C4" t="s">
-        <v>280</v>
+        <v>286</v>
       </c>
     </row>
     <row r="5" spans="3:3">
       <c r="C5" t="s">
-        <v>281</v>
+        <v>287</v>
       </c>
     </row>
     <row r="6" spans="4:4">
       <c r="D6" t="s">
-        <v>282</v>
+        <v>288</v>
       </c>
     </row>
     <row r="7" spans="4:4">
       <c r="D7" t="s">
-        <v>283</v>
+        <v>289</v>
       </c>
     </row>
     <row r="8" spans="3:3">
       <c r="C8" t="s">
-        <v>284</v>
+        <v>290</v>
       </c>
     </row>
     <row r="9" spans="3:3">
       <c r="C9" t="s">
-        <v>285</v>
+        <v>291</v>
       </c>
     </row>
     <row r="10" spans="3:3">
       <c r="C10" t="s">
-        <v>286</v>
+        <v>292</v>
       </c>
     </row>
     <row r="11" spans="3:3">
       <c r="C11" t="s">
-        <v>287</v>
+        <v>293</v>
       </c>
     </row>
     <row r="12" spans="2:2">
       <c r="B12" t="s">
-        <v>288</v>
+        <v>294</v>
       </c>
     </row>
     <row r="13" spans="3:3">
       <c r="C13" t="s">
-        <v>289</v>
+        <v>295</v>
       </c>
     </row>
     <row r="14" spans="4:4">
       <c r="D14" t="s">
-        <v>290</v>
+        <v>296</v>
       </c>
     </row>
     <row r="15" spans="4:4">
       <c r="D15" t="s">
-        <v>291</v>
+        <v>297</v>
       </c>
     </row>
     <row r="16" spans="3:3">
       <c r="C16" t="s">
-        <v>292</v>
+        <v>298</v>
       </c>
     </row>
     <row r="17" spans="4:4">
       <c r="D17" t="s">
-        <v>293</v>
+        <v>299</v>
       </c>
     </row>
     <row r="18" spans="5:5">
       <c r="E18" t="s">
-        <v>294</v>
+        <v>300</v>
       </c>
     </row>
     <row r="19" spans="5:5">
       <c r="E19" t="s">
-        <v>295</v>
+        <v>301</v>
       </c>
     </row>
     <row r="20" spans="5:5">
       <c r="E20" t="s">
-        <v>296</v>
+        <v>302</v>
       </c>
     </row>
     <row r="21" spans="4:4">
       <c r="D21" t="s">
-        <v>297</v>
+        <v>303</v>
       </c>
     </row>
     <row r="22" spans="5:5">
       <c r="E22" t="s">
-        <v>298</v>
+        <v>304</v>
       </c>
     </row>
     <row r="23" spans="5:5">
       <c r="E23" t="s">
-        <v>299</v>
+        <v>305</v>
       </c>
     </row>
     <row r="24" spans="2:2">
       <c r="B24" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
     </row>
     <row r="25" spans="2:2">
       <c r="B25" t="s">
-        <v>301</v>
+        <v>307</v>
       </c>
     </row>
     <row r="26" spans="2:2">
       <c r="B26" t="s">
-        <v>302</v>
+        <v>308</v>
       </c>
     </row>
     <row r="27" spans="3:3">
       <c r="C27" t="s">
-        <v>303</v>
+        <v>309</v>
       </c>
     </row>
     <row r="28" spans="3:3">
       <c r="C28" t="s">
-        <v>304</v>
+        <v>310</v>
       </c>
     </row>
     <row r="29" spans="3:3">
       <c r="C29" s="3" t="s">
-        <v>305</v>
+        <v>311</v>
       </c>
     </row>
     <row r="30" spans="4:4">
       <c r="D30" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
     </row>
     <row r="31" spans="4:4">
       <c r="D31" t="s">
-        <v>307</v>
+        <v>313</v>
       </c>
     </row>
     <row r="32" spans="4:4">
       <c r="D32" t="s">
-        <v>308</v>
+        <v>314</v>
       </c>
     </row>
     <row r="33" spans="4:4">
       <c r="D33" t="s">
-        <v>309</v>
+        <v>315</v>
       </c>
     </row>
     <row r="34" spans="5:5">
       <c r="E34" t="s">
-        <v>310</v>
+        <v>316</v>
       </c>
     </row>
     <row r="35" spans="5:5">
       <c r="E35" t="s">
-        <v>311</v>
+        <v>317</v>
       </c>
     </row>
     <row r="36" spans="3:3">
       <c r="C36" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
     </row>
     <row r="37" spans="4:4">
       <c r="D37" t="s">
-        <v>313</v>
+        <v>319</v>
       </c>
     </row>
     <row r="38" spans="4:4">
       <c r="D38" t="s">
-        <v>314</v>
+        <v>320</v>
       </c>
     </row>
     <row r="39" spans="4:4">
       <c r="D39" t="s">
-        <v>308</v>
+        <v>314</v>
       </c>
     </row>
     <row r="40" spans="4:4">
       <c r="D40" t="s">
-        <v>309</v>
+        <v>315</v>
       </c>
     </row>
     <row r="41" spans="5:5">
       <c r="E41" t="s">
-        <v>310</v>
+        <v>316</v>
       </c>
     </row>
     <row r="42" spans="5:5">
       <c r="E42" t="s">
-        <v>311</v>
+        <v>317</v>
       </c>
     </row>
     <row r="43" spans="4:4">
       <c r="D43" t="s">
-        <v>315</v>
+        <v>321</v>
       </c>
     </row>
     <row r="44" spans="5:5">
       <c r="E44" t="s">
-        <v>316</v>
+        <v>322</v>
       </c>
     </row>
     <row r="45" spans="5:5">
       <c r="E45" t="s">
-        <v>317</v>
+        <v>323</v>
       </c>
     </row>
     <row r="46" spans="6:6">
       <c r="F46" t="s">
-        <v>318</v>
+        <v>324</v>
       </c>
     </row>
     <row r="47" spans="6:6">
       <c r="F47" t="s">
-        <v>319</v>
+        <v>325</v>
       </c>
     </row>
     <row r="48" spans="2:2">
       <c r="B48" t="s">
-        <v>320</v>
+        <v>326</v>
       </c>
     </row>
     <row r="49" spans="3:3">
       <c r="C49" t="s">
-        <v>321</v>
+        <v>327</v>
       </c>
     </row>
     <row r="50" spans="3:3">
       <c r="C50" t="s">
-        <v>322</v>
+        <v>328</v>
       </c>
     </row>
     <row r="51" spans="2:2">
       <c r="B51" t="s">
-        <v>323</v>
+        <v>329</v>
       </c>
     </row>
     <row r="52" spans="3:3">
       <c r="C52" t="s">
-        <v>324</v>
+        <v>330</v>
       </c>
     </row>
     <row r="53" spans="3:3">
       <c r="C53" t="s">
-        <v>325</v>
+        <v>331</v>
       </c>
     </row>
     <row r="54" spans="3:3">
       <c r="C54" t="s">
-        <v>326</v>
+        <v>332</v>
       </c>
     </row>
     <row r="55" spans="3:3">
       <c r="C55" t="s">
-        <v>327</v>
+        <v>333</v>
       </c>
     </row>
     <row r="56" spans="3:3">
       <c r="C56" t="s">
-        <v>328</v>
+        <v>334</v>
       </c>
     </row>
     <row r="57" spans="3:3">
       <c r="C57" t="s">
-        <v>329</v>
+        <v>335</v>
       </c>
     </row>
   </sheetData>
@@ -6100,62 +6163,62 @@
         <v>20240411</v>
       </c>
       <c r="B2" t="s">
-        <v>330</v>
+        <v>336</v>
       </c>
     </row>
     <row r="3" s="4" customFormat="1" spans="2:2">
       <c r="B3" s="4" t="s">
-        <v>331</v>
+        <v>337</v>
       </c>
     </row>
     <row r="4" s="4" customFormat="1" spans="3:3">
       <c r="C4" s="4" t="s">
-        <v>332</v>
+        <v>338</v>
       </c>
     </row>
     <row r="5" s="4" customFormat="1" spans="3:3">
       <c r="C5" s="4" t="s">
-        <v>333</v>
+        <v>339</v>
       </c>
     </row>
     <row r="6" s="4" customFormat="1" spans="3:3">
       <c r="C6" s="4" t="s">
-        <v>334</v>
+        <v>340</v>
       </c>
     </row>
     <row r="7" spans="3:3">
       <c r="C7" s="4" t="s">
-        <v>335</v>
+        <v>341</v>
       </c>
     </row>
     <row r="8" spans="2:2">
       <c r="B8" t="s">
-        <v>336</v>
+        <v>342</v>
       </c>
     </row>
     <row r="9" spans="3:3">
       <c r="C9" t="s">
-        <v>337</v>
+        <v>343</v>
       </c>
     </row>
     <row r="10" spans="3:3">
       <c r="C10" t="s">
-        <v>338</v>
+        <v>344</v>
       </c>
     </row>
     <row r="11" spans="4:4">
       <c r="D11" t="s">
-        <v>339</v>
+        <v>345</v>
       </c>
     </row>
     <row r="12" spans="4:4">
       <c r="D12" t="s">
-        <v>340</v>
+        <v>346</v>
       </c>
     </row>
     <row r="13" spans="2:2">
       <c r="B13" t="s">
-        <v>341</v>
+        <v>347</v>
       </c>
     </row>
   </sheetData>
@@ -6209,97 +6272,97 @@
         <v>20240412</v>
       </c>
       <c r="B2" t="s">
-        <v>342</v>
+        <v>348</v>
       </c>
     </row>
     <row r="3" spans="2:2">
       <c r="B3" t="s">
-        <v>343</v>
+        <v>349</v>
       </c>
     </row>
     <row r="4" spans="3:3">
       <c r="C4" t="s">
-        <v>344</v>
+        <v>350</v>
       </c>
     </row>
     <row r="5" spans="3:3">
       <c r="C5" t="s">
-        <v>345</v>
+        <v>351</v>
       </c>
     </row>
     <row r="6" spans="3:3">
       <c r="C6" t="s">
-        <v>346</v>
+        <v>352</v>
       </c>
     </row>
     <row r="7" spans="3:3">
       <c r="C7" t="s">
-        <v>347</v>
+        <v>353</v>
       </c>
     </row>
     <row r="8" spans="4:4">
       <c r="D8" t="s">
-        <v>348</v>
+        <v>354</v>
       </c>
     </row>
     <row r="9" spans="4:4">
       <c r="D9" t="s">
-        <v>349</v>
+        <v>355</v>
       </c>
     </row>
     <row r="10" spans="3:3">
       <c r="C10" t="s">
-        <v>350</v>
+        <v>356</v>
       </c>
     </row>
     <row r="11" spans="2:2">
       <c r="B11" t="s">
-        <v>351</v>
+        <v>357</v>
       </c>
     </row>
     <row r="12" spans="2:2">
       <c r="B12" t="s">
-        <v>352</v>
+        <v>358</v>
       </c>
     </row>
     <row r="13" spans="3:3">
       <c r="C13" t="s">
-        <v>353</v>
+        <v>359</v>
       </c>
     </row>
     <row r="14" spans="3:3">
       <c r="C14" t="s">
-        <v>354</v>
+        <v>360</v>
       </c>
     </row>
     <row r="15" spans="3:3">
       <c r="C15" t="s">
-        <v>355</v>
+        <v>361</v>
       </c>
     </row>
     <row r="16" spans="2:2">
       <c r="B16" t="s">
-        <v>356</v>
+        <v>362</v>
       </c>
     </row>
     <row r="17" spans="2:2">
       <c r="B17" t="s">
-        <v>357</v>
+        <v>363</v>
       </c>
     </row>
     <row r="18" spans="3:3">
       <c r="C18" t="s">
-        <v>358</v>
+        <v>364</v>
       </c>
     </row>
     <row r="19" spans="3:3">
       <c r="C19" t="s">
-        <v>359</v>
+        <v>365</v>
       </c>
     </row>
     <row r="20" spans="3:3">
       <c r="C20" t="s">
-        <v>360</v>
+        <v>366</v>
       </c>
     </row>
   </sheetData>
@@ -6353,247 +6416,247 @@
         <v>20240413</v>
       </c>
       <c r="B2" t="s">
-        <v>361</v>
+        <v>367</v>
       </c>
     </row>
     <row r="3" spans="3:3">
       <c r="C3" t="s">
-        <v>362</v>
+        <v>368</v>
       </c>
     </row>
     <row r="4" spans="4:4">
       <c r="D4" t="s">
-        <v>363</v>
+        <v>369</v>
       </c>
     </row>
     <row r="5" spans="4:4">
       <c r="D5" t="s">
-        <v>364</v>
+        <v>370</v>
       </c>
     </row>
     <row r="6" s="4" customFormat="1" spans="3:3">
       <c r="C6" s="4" t="s">
-        <v>365</v>
+        <v>371</v>
       </c>
     </row>
     <row r="7" spans="2:2">
       <c r="B7" t="s">
-        <v>366</v>
+        <v>372</v>
       </c>
     </row>
     <row r="8" spans="2:2">
       <c r="B8" t="s">
-        <v>367</v>
+        <v>373</v>
       </c>
     </row>
     <row r="9" spans="3:3">
       <c r="C9" t="s">
-        <v>368</v>
+        <v>374</v>
       </c>
     </row>
     <row r="10" spans="4:4">
       <c r="D10" t="s">
-        <v>369</v>
+        <v>375</v>
       </c>
     </row>
     <row r="11" spans="4:4">
       <c r="D11" t="s">
-        <v>370</v>
+        <v>376</v>
       </c>
     </row>
     <row r="12" spans="4:4">
       <c r="D12" t="s">
-        <v>371</v>
+        <v>377</v>
       </c>
     </row>
     <row r="13" spans="5:5">
       <c r="E13" t="s">
-        <v>372</v>
+        <v>378</v>
       </c>
     </row>
     <row r="14" spans="5:5">
       <c r="E14" t="s">
-        <v>373</v>
+        <v>379</v>
       </c>
     </row>
     <row r="15" spans="2:2">
       <c r="B15" t="s">
-        <v>374</v>
+        <v>380</v>
       </c>
     </row>
     <row r="16" spans="3:3">
       <c r="C16" t="s">
-        <v>375</v>
+        <v>381</v>
       </c>
     </row>
     <row r="17" spans="3:3">
       <c r="C17" t="s">
-        <v>376</v>
+        <v>382</v>
       </c>
     </row>
     <row r="18" spans="4:4">
       <c r="D18" t="s">
-        <v>377</v>
+        <v>383</v>
       </c>
     </row>
     <row r="19" spans="3:3">
       <c r="C19" t="s">
-        <v>378</v>
+        <v>384</v>
       </c>
     </row>
     <row r="20" spans="3:3">
       <c r="C20" t="s">
-        <v>379</v>
+        <v>385</v>
       </c>
     </row>
     <row r="21" spans="4:4">
       <c r="D21" t="s">
-        <v>380</v>
+        <v>386</v>
       </c>
     </row>
     <row r="22" spans="4:4">
       <c r="D22" t="s">
-        <v>381</v>
+        <v>387</v>
       </c>
     </row>
     <row r="23" spans="2:2">
       <c r="B23" t="s">
-        <v>382</v>
+        <v>388</v>
       </c>
     </row>
     <row r="24" spans="3:3">
       <c r="C24" t="s">
-        <v>383</v>
+        <v>389</v>
       </c>
     </row>
     <row r="25" spans="4:4">
       <c r="D25" t="s">
-        <v>384</v>
+        <v>390</v>
       </c>
     </row>
     <row r="26" spans="5:5">
       <c r="E26" t="s">
-        <v>385</v>
+        <v>391</v>
       </c>
     </row>
     <row r="27" spans="5:5">
       <c r="E27" t="s">
-        <v>386</v>
+        <v>392</v>
       </c>
     </row>
     <row r="28" spans="4:4">
       <c r="D28" t="s">
-        <v>387</v>
+        <v>393</v>
       </c>
     </row>
     <row r="29" spans="4:4">
       <c r="D29" t="s">
-        <v>388</v>
+        <v>394</v>
       </c>
     </row>
     <row r="30" spans="3:3">
       <c r="C30" t="s">
-        <v>389</v>
+        <v>395</v>
       </c>
     </row>
     <row r="31" spans="4:4">
       <c r="D31" t="s">
-        <v>390</v>
+        <v>396</v>
       </c>
     </row>
     <row r="32" spans="5:5">
       <c r="E32" t="s">
-        <v>391</v>
+        <v>397</v>
       </c>
     </row>
     <row r="33" spans="4:4">
       <c r="D33" t="s">
-        <v>392</v>
+        <v>398</v>
       </c>
     </row>
     <row r="34" spans="5:5">
       <c r="E34" t="s">
-        <v>393</v>
+        <v>399</v>
       </c>
     </row>
     <row r="35" spans="3:3">
       <c r="C35" t="s">
-        <v>394</v>
+        <v>400</v>
       </c>
     </row>
     <row r="36" spans="4:4">
       <c r="D36" t="s">
-        <v>395</v>
+        <v>401</v>
       </c>
     </row>
     <row r="37" spans="4:4">
       <c r="D37" t="s">
-        <v>396</v>
+        <v>402</v>
       </c>
     </row>
     <row r="38" spans="4:4">
       <c r="D38" t="s">
-        <v>397</v>
+        <v>403</v>
       </c>
     </row>
     <row r="39" spans="4:4">
       <c r="D39" t="s">
-        <v>398</v>
+        <v>404</v>
       </c>
     </row>
     <row r="40" spans="2:2">
       <c r="B40" t="s">
-        <v>399</v>
+        <v>405</v>
       </c>
     </row>
     <row r="41" spans="3:3">
       <c r="C41" t="s">
-        <v>400</v>
+        <v>406</v>
       </c>
     </row>
     <row r="42" spans="3:3">
       <c r="C42" t="s">
-        <v>401</v>
+        <v>407</v>
       </c>
     </row>
     <row r="43" spans="3:3">
       <c r="C43" t="s">
-        <v>402</v>
+        <v>408</v>
       </c>
     </row>
     <row r="44" spans="3:3">
       <c r="C44" t="s">
-        <v>403</v>
+        <v>409</v>
       </c>
     </row>
     <row r="45" spans="2:2">
       <c r="B45" t="s">
-        <v>404</v>
+        <v>410</v>
       </c>
     </row>
     <row r="46" spans="3:3">
       <c r="C46" t="s">
-        <v>405</v>
+        <v>411</v>
       </c>
     </row>
     <row r="47" spans="4:4">
       <c r="D47" t="s">
-        <v>406</v>
+        <v>412</v>
       </c>
     </row>
     <row r="48" spans="4:4">
       <c r="D48" t="s">
-        <v>407</v>
+        <v>413</v>
       </c>
     </row>
     <row r="49" spans="3:3">
       <c r="C49" t="s">
-        <v>408</v>
+        <v>414</v>
       </c>
     </row>
     <row r="50" spans="3:3">
       <c r="C50" t="s">
-        <v>409</v>
+        <v>415</v>
       </c>
     </row>
   </sheetData>
@@ -6650,142 +6713,142 @@
         <v>20240414</v>
       </c>
       <c r="B2" t="s">
-        <v>410</v>
+        <v>416</v>
       </c>
     </row>
     <row r="3" spans="3:3">
       <c r="C3" t="s">
-        <v>411</v>
+        <v>417</v>
       </c>
     </row>
     <row r="4" spans="3:3">
       <c r="C4" t="s">
-        <v>412</v>
+        <v>418</v>
       </c>
     </row>
     <row r="5" spans="3:3">
       <c r="C5" t="s">
-        <v>413</v>
+        <v>419</v>
       </c>
     </row>
     <row r="6" spans="2:2">
       <c r="B6" t="s">
-        <v>414</v>
+        <v>420</v>
       </c>
     </row>
     <row r="7" spans="3:3">
       <c r="C7" t="s">
-        <v>415</v>
+        <v>421</v>
       </c>
     </row>
     <row r="8" spans="3:3">
       <c r="C8" t="s">
-        <v>416</v>
+        <v>422</v>
       </c>
     </row>
     <row r="9" spans="3:3">
       <c r="C9" t="s">
-        <v>417</v>
+        <v>423</v>
       </c>
     </row>
     <row r="10" spans="3:3">
       <c r="C10" t="s">
-        <v>418</v>
+        <v>424</v>
       </c>
     </row>
     <row r="11" spans="4:4">
       <c r="D11" t="s">
-        <v>419</v>
+        <v>425</v>
       </c>
     </row>
     <row r="12" spans="4:4">
       <c r="D12" t="s">
-        <v>420</v>
+        <v>426</v>
       </c>
     </row>
     <row r="13" spans="2:2">
       <c r="B13" t="s">
-        <v>421</v>
+        <v>427</v>
       </c>
     </row>
     <row r="14" spans="3:3">
       <c r="C14" t="s">
-        <v>422</v>
+        <v>428</v>
       </c>
     </row>
     <row r="15" spans="3:3">
       <c r="C15" t="s">
-        <v>423</v>
+        <v>429</v>
       </c>
     </row>
     <row r="16" spans="3:3">
       <c r="C16" t="s">
-        <v>424</v>
+        <v>430</v>
       </c>
     </row>
     <row r="17" spans="2:2">
       <c r="B17" t="s">
-        <v>425</v>
+        <v>431</v>
       </c>
     </row>
     <row r="18" spans="3:3">
       <c r="C18" t="s">
-        <v>426</v>
+        <v>432</v>
       </c>
     </row>
     <row r="19" spans="3:3">
       <c r="C19" t="s">
-        <v>427</v>
+        <v>433</v>
       </c>
     </row>
     <row r="20" spans="3:3">
       <c r="C20" t="s">
-        <v>428</v>
+        <v>434</v>
       </c>
     </row>
     <row r="21" spans="3:3">
       <c r="C21" t="s">
-        <v>429</v>
+        <v>435</v>
       </c>
     </row>
     <row r="22" spans="3:3">
       <c r="C22" t="s">
-        <v>430</v>
+        <v>436</v>
       </c>
     </row>
     <row r="23" spans="2:2">
       <c r="B23" t="s">
-        <v>431</v>
+        <v>437</v>
       </c>
     </row>
     <row r="24" spans="3:3">
       <c r="C24" t="s">
-        <v>432</v>
+        <v>438</v>
       </c>
     </row>
     <row r="25" s="4" customFormat="1" spans="4:4">
       <c r="D25" s="4" t="s">
-        <v>433</v>
+        <v>439</v>
       </c>
     </row>
     <row r="26" spans="3:3">
       <c r="C26" t="s">
-        <v>434</v>
+        <v>440</v>
       </c>
     </row>
     <row r="27" s="4" customFormat="1" spans="4:4">
       <c r="D27" s="4" t="s">
-        <v>435</v>
+        <v>441</v>
       </c>
     </row>
     <row r="28" spans="3:3">
       <c r="C28" t="s">
-        <v>436</v>
+        <v>442</v>
       </c>
     </row>
     <row r="29" spans="4:4">
       <c r="D29" t="s">
-        <v>437</v>
+        <v>443</v>
       </c>
     </row>
   </sheetData>
@@ -6842,122 +6905,122 @@
         <v>20240415</v>
       </c>
       <c r="B2" t="s">
-        <v>438</v>
+        <v>444</v>
       </c>
     </row>
     <row r="3" spans="3:3">
       <c r="C3" t="s">
-        <v>439</v>
+        <v>445</v>
       </c>
     </row>
     <row r="4" spans="3:3">
       <c r="C4" t="s">
-        <v>440</v>
+        <v>446</v>
       </c>
     </row>
     <row r="5" spans="3:3">
       <c r="C5" t="s">
-        <v>441</v>
+        <v>447</v>
       </c>
     </row>
     <row r="6" spans="4:4">
       <c r="D6" t="s">
-        <v>442</v>
+        <v>448</v>
       </c>
     </row>
     <row r="7" spans="2:2">
       <c r="B7" t="s">
-        <v>443</v>
+        <v>449</v>
       </c>
     </row>
     <row r="8" spans="3:3">
       <c r="C8" t="s">
-        <v>444</v>
+        <v>450</v>
       </c>
     </row>
     <row r="9" spans="4:4">
       <c r="D9" t="s">
-        <v>445</v>
+        <v>451</v>
       </c>
     </row>
     <row r="10" spans="4:4">
       <c r="D10" t="s">
-        <v>446</v>
+        <v>452</v>
       </c>
     </row>
     <row r="11" spans="3:3">
       <c r="C11" t="s">
-        <v>447</v>
+        <v>453</v>
       </c>
     </row>
     <row r="12" spans="3:3">
       <c r="C12" t="s">
-        <v>448</v>
+        <v>454</v>
       </c>
     </row>
     <row r="13" spans="4:4">
       <c r="D13" t="s">
-        <v>449</v>
+        <v>455</v>
       </c>
     </row>
     <row r="14" spans="4:4">
       <c r="D14" t="s">
-        <v>450</v>
+        <v>456</v>
       </c>
     </row>
     <row r="15" spans="2:2">
       <c r="B15" t="s">
-        <v>451</v>
+        <v>457</v>
       </c>
     </row>
     <row r="16" spans="3:3">
       <c r="C16" t="s">
-        <v>452</v>
+        <v>458</v>
       </c>
     </row>
     <row r="17" spans="4:4">
       <c r="D17" t="s">
-        <v>453</v>
+        <v>459</v>
       </c>
     </row>
     <row r="18" spans="4:4">
       <c r="D18" t="s">
-        <v>454</v>
+        <v>460</v>
       </c>
     </row>
     <row r="19" spans="3:3">
       <c r="C19" t="s">
-        <v>455</v>
+        <v>461</v>
       </c>
     </row>
     <row r="20" spans="4:4">
       <c r="D20" t="s">
-        <v>456</v>
+        <v>462</v>
       </c>
     </row>
     <row r="21" spans="4:4">
       <c r="D21" t="s">
-        <v>457</v>
+        <v>463</v>
       </c>
     </row>
     <row r="22" spans="4:4">
       <c r="D22" t="s">
-        <v>458</v>
+        <v>464</v>
       </c>
     </row>
     <row r="23" spans="5:5">
       <c r="E23" t="s">
-        <v>459</v>
+        <v>465</v>
       </c>
     </row>
     <row r="24" spans="5:5">
       <c r="E24" t="s">
-        <v>460</v>
+        <v>466</v>
       </c>
     </row>
     <row r="25" spans="3:3">
       <c r="C25" t="s">
-        <v>461</v>
+        <v>467</v>
       </c>
     </row>
   </sheetData>
@@ -7014,67 +7077,67 @@
         <v>20240416</v>
       </c>
       <c r="B2" t="s">
-        <v>462</v>
+        <v>468</v>
       </c>
     </row>
     <row r="3" spans="3:3">
       <c r="C3" t="s">
-        <v>463</v>
+        <v>469</v>
       </c>
     </row>
     <row r="4" spans="3:3">
       <c r="C4" t="s">
-        <v>464</v>
+        <v>470</v>
       </c>
     </row>
     <row r="5" spans="2:2">
       <c r="B5" t="s">
-        <v>465</v>
+        <v>471</v>
       </c>
     </row>
     <row r="6" spans="3:3">
       <c r="C6" t="s">
-        <v>466</v>
+        <v>472</v>
       </c>
     </row>
     <row r="7" spans="4:4">
       <c r="D7" t="s">
-        <v>467</v>
+        <v>473</v>
       </c>
     </row>
     <row r="8" spans="4:4">
       <c r="D8" t="s">
-        <v>468</v>
+        <v>474</v>
       </c>
     </row>
     <row r="9" spans="4:4">
       <c r="D9" t="s">
-        <v>469</v>
+        <v>475</v>
       </c>
     </row>
     <row r="10" spans="3:3">
       <c r="C10" t="s">
-        <v>470</v>
+        <v>476</v>
       </c>
     </row>
     <row r="11" spans="4:4">
       <c r="D11" t="s">
-        <v>471</v>
+        <v>477</v>
       </c>
     </row>
     <row r="12" spans="4:4">
       <c r="D12" t="s">
-        <v>472</v>
+        <v>478</v>
       </c>
     </row>
     <row r="13" spans="5:5">
       <c r="E13" t="s">
-        <v>473</v>
+        <v>479</v>
       </c>
     </row>
     <row r="14" spans="4:4">
       <c r="D14" t="s">
-        <v>474</v>
+        <v>480</v>
       </c>
     </row>
   </sheetData>
@@ -7131,107 +7194,107 @@
         <v>20240417</v>
       </c>
       <c r="B2" t="s">
-        <v>475</v>
+        <v>481</v>
       </c>
     </row>
     <row r="3" spans="3:3">
       <c r="C3" t="s">
-        <v>476</v>
+        <v>482</v>
       </c>
     </row>
     <row r="4" spans="4:4">
       <c r="D4" t="s">
-        <v>477</v>
+        <v>483</v>
       </c>
     </row>
     <row r="5" spans="3:3">
       <c r="C5" t="s">
-        <v>478</v>
+        <v>484</v>
       </c>
     </row>
     <row r="6" spans="4:4">
       <c r="D6" t="s">
-        <v>479</v>
+        <v>485</v>
       </c>
     </row>
     <row r="7" spans="2:2">
       <c r="B7" t="s">
-        <v>480</v>
+        <v>486</v>
       </c>
     </row>
     <row r="8" spans="3:3">
       <c r="C8" t="s">
-        <v>481</v>
+        <v>487</v>
       </c>
     </row>
     <row r="9" spans="3:3">
       <c r="C9" t="s">
-        <v>482</v>
+        <v>488</v>
       </c>
     </row>
     <row r="10" spans="3:3">
       <c r="C10" t="s">
-        <v>483</v>
+        <v>489</v>
       </c>
     </row>
     <row r="11" spans="4:4">
       <c r="D11" t="s">
-        <v>484</v>
+        <v>490</v>
       </c>
     </row>
     <row r="12" spans="4:4">
       <c r="D12" t="s">
-        <v>485</v>
+        <v>491</v>
       </c>
     </row>
     <row r="13" spans="3:3">
       <c r="C13" t="s">
-        <v>486</v>
+        <v>492</v>
       </c>
     </row>
     <row r="14" spans="3:3">
       <c r="C14" t="s">
-        <v>487</v>
+        <v>493</v>
       </c>
     </row>
     <row r="15" spans="4:4">
       <c r="D15" t="s">
-        <v>488</v>
+        <v>494</v>
       </c>
     </row>
     <row r="16" spans="4:4">
       <c r="D16" t="s">
-        <v>489</v>
+        <v>495</v>
       </c>
     </row>
     <row r="17" spans="4:4">
       <c r="D17" t="s">
-        <v>490</v>
+        <v>496</v>
       </c>
     </row>
     <row r="18" spans="4:4">
       <c r="D18" t="s">
-        <v>491</v>
+        <v>497</v>
       </c>
     </row>
     <row r="19" spans="2:2">
       <c r="B19" t="s">
-        <v>492</v>
+        <v>498</v>
       </c>
     </row>
     <row r="20" spans="2:2">
       <c r="B20" t="s">
-        <v>493</v>
+        <v>499</v>
       </c>
     </row>
     <row r="21" spans="2:2">
       <c r="B21" t="s">
-        <v>494</v>
+        <v>500</v>
       </c>
     </row>
     <row r="22" spans="3:3">
       <c r="C22" t="s">
-        <v>495</v>
+        <v>501</v>
       </c>
     </row>
   </sheetData>
@@ -7288,112 +7351,112 @@
         <v>20240418</v>
       </c>
       <c r="B2" t="s">
-        <v>496</v>
+        <v>502</v>
       </c>
     </row>
     <row r="3" spans="3:3">
       <c r="C3" t="s">
-        <v>497</v>
+        <v>503</v>
       </c>
     </row>
     <row r="4" spans="3:3">
       <c r="C4" t="s">
-        <v>498</v>
+        <v>504</v>
       </c>
     </row>
     <row r="5" spans="3:3">
       <c r="C5" t="s">
-        <v>499</v>
+        <v>505</v>
       </c>
     </row>
     <row r="6" spans="3:3">
       <c r="C6" t="s">
-        <v>500</v>
+        <v>506</v>
       </c>
     </row>
     <row r="7" spans="2:2">
       <c r="B7" t="s">
-        <v>501</v>
+        <v>507</v>
       </c>
     </row>
     <row r="8" spans="3:3">
       <c r="C8" t="s">
-        <v>502</v>
+        <v>508</v>
       </c>
     </row>
     <row r="9" spans="3:3">
       <c r="C9" t="s">
-        <v>503</v>
+        <v>509</v>
       </c>
     </row>
     <row r="10" spans="3:3">
       <c r="C10" t="s">
-        <v>504</v>
+        <v>510</v>
       </c>
     </row>
     <row r="11" spans="4:4">
       <c r="D11" t="s">
-        <v>505</v>
+        <v>511</v>
       </c>
     </row>
     <row r="12" spans="4:4">
       <c r="D12" t="s">
-        <v>506</v>
+        <v>512</v>
       </c>
     </row>
     <row r="13" spans="2:2">
       <c r="B13" t="s">
-        <v>507</v>
+        <v>513</v>
       </c>
     </row>
     <row r="14" spans="3:3">
       <c r="C14" t="s">
-        <v>508</v>
+        <v>514</v>
       </c>
     </row>
     <row r="15" spans="4:4">
       <c r="D15" t="s">
-        <v>509</v>
+        <v>515</v>
       </c>
     </row>
     <row r="16" spans="4:4">
       <c r="D16" t="s">
-        <v>510</v>
+        <v>516</v>
       </c>
     </row>
     <row r="17" spans="3:3">
       <c r="C17" t="s">
-        <v>511</v>
+        <v>517</v>
       </c>
     </row>
     <row r="18" spans="3:3">
       <c r="C18" t="s">
-        <v>512</v>
+        <v>518</v>
       </c>
     </row>
     <row r="19" spans="3:3">
       <c r="C19" t="s">
-        <v>513</v>
+        <v>519</v>
       </c>
     </row>
     <row r="20" spans="3:3">
       <c r="C20" t="s">
-        <v>514</v>
+        <v>520</v>
       </c>
     </row>
     <row r="21" spans="2:2">
       <c r="B21" t="s">
-        <v>515</v>
+        <v>521</v>
       </c>
     </row>
     <row r="22" spans="2:2">
       <c r="B22" t="s">
-        <v>516</v>
+        <v>522</v>
       </c>
     </row>
     <row r="23" spans="2:2">
       <c r="B23" t="s">
-        <v>517</v>
+        <v>523</v>
       </c>
     </row>
   </sheetData>
@@ -7450,28 +7513,28 @@
         <v>20240304</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="C2" s="3"/>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="3"/>
       <c r="B3" s="3" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C3" s="3"/>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="3"/>
       <c r="B4" s="3" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="C4" s="3"/>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="3"/>
       <c r="B5" s="3" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="C5" s="3"/>
     </row>
@@ -7479,20 +7542,20 @@
       <c r="A6" s="3"/>
       <c r="B6" s="3"/>
       <c r="C6" s="3" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="3"/>
       <c r="B7" s="3"/>
       <c r="C7" s="3" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="3"/>
       <c r="B8" s="3" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C8" s="3"/>
     </row>
@@ -7500,40 +7563,40 @@
       <c r="A9" s="3"/>
       <c r="B9" s="3"/>
       <c r="C9" s="3" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10" s="3"/>
       <c r="B10" s="3"/>
       <c r="C10" s="3" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="3"/>
       <c r="B11" s="3"/>
       <c r="C11" s="3" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="3"/>
       <c r="B12" s="3"/>
       <c r="C12" s="3" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="3"/>
       <c r="C13" s="3" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
     </row>
     <row r="14" spans="1:4">
       <c r="A14" s="3"/>
       <c r="D14" s="3" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
     </row>
     <row r="15" spans="4:4">
@@ -7593,177 +7656,177 @@
         <v>20240420</v>
       </c>
       <c r="B2" t="s">
-        <v>518</v>
+        <v>524</v>
       </c>
     </row>
     <row r="3" spans="3:3">
       <c r="C3" t="s">
-        <v>519</v>
+        <v>525</v>
       </c>
     </row>
     <row r="4" spans="3:3">
       <c r="C4" t="s">
-        <v>520</v>
+        <v>526</v>
       </c>
     </row>
     <row r="5" spans="2:2">
       <c r="B5" t="s">
-        <v>521</v>
+        <v>527</v>
       </c>
     </row>
     <row r="6" spans="3:3">
       <c r="C6" t="s">
-        <v>522</v>
+        <v>528</v>
       </c>
     </row>
     <row r="7" spans="2:2">
       <c r="B7" t="s">
-        <v>523</v>
+        <v>529</v>
       </c>
     </row>
     <row r="8" spans="2:2">
       <c r="B8" t="s">
-        <v>524</v>
+        <v>530</v>
       </c>
     </row>
     <row r="9" spans="3:3">
       <c r="C9" t="s">
-        <v>525</v>
+        <v>531</v>
       </c>
     </row>
     <row r="10" spans="4:4">
       <c r="D10" t="s">
-        <v>526</v>
+        <v>532</v>
       </c>
     </row>
     <row r="11" spans="3:3">
       <c r="C11" t="s">
-        <v>527</v>
+        <v>533</v>
       </c>
     </row>
     <row r="12" spans="3:3">
       <c r="C12" t="s">
-        <v>528</v>
+        <v>534</v>
       </c>
     </row>
     <row r="13" spans="4:4">
       <c r="D13" t="s">
-        <v>529</v>
+        <v>535</v>
       </c>
     </row>
     <row r="14" spans="4:4">
       <c r="D14" t="s">
-        <v>530</v>
+        <v>536</v>
       </c>
     </row>
     <row r="15" spans="2:2">
       <c r="B15" t="s">
-        <v>531</v>
+        <v>537</v>
       </c>
     </row>
     <row r="16" spans="3:3">
       <c r="C16" t="s">
-        <v>532</v>
+        <v>538</v>
       </c>
     </row>
     <row r="17" spans="4:4">
       <c r="D17" t="s">
-        <v>533</v>
+        <v>539</v>
       </c>
     </row>
     <row r="18" spans="5:5">
       <c r="E18" t="s">
-        <v>534</v>
+        <v>540</v>
       </c>
     </row>
     <row r="19" spans="5:5">
       <c r="E19" t="s">
-        <v>535</v>
+        <v>541</v>
       </c>
     </row>
     <row r="20" spans="4:4">
       <c r="D20" t="s">
-        <v>536</v>
+        <v>542</v>
       </c>
     </row>
     <row r="21" spans="5:5">
       <c r="E21" t="s">
-        <v>537</v>
+        <v>543</v>
       </c>
     </row>
     <row r="22" spans="5:5">
       <c r="E22" t="s">
-        <v>538</v>
+        <v>544</v>
       </c>
     </row>
     <row r="23" spans="5:5">
       <c r="E23" t="s">
-        <v>539</v>
+        <v>545</v>
       </c>
     </row>
     <row r="24" spans="5:5">
       <c r="E24" t="s">
-        <v>540</v>
+        <v>546</v>
       </c>
     </row>
     <row r="25" spans="2:2">
       <c r="B25" t="s">
-        <v>541</v>
+        <v>547</v>
       </c>
     </row>
     <row r="26" spans="3:3">
       <c r="C26" t="s">
-        <v>542</v>
+        <v>548</v>
       </c>
     </row>
     <row r="27" spans="3:3">
       <c r="C27" t="s">
-        <v>543</v>
+        <v>549</v>
       </c>
     </row>
     <row r="28" spans="3:3">
       <c r="C28" t="s">
-        <v>544</v>
+        <v>550</v>
       </c>
     </row>
     <row r="29" spans="4:4">
       <c r="D29" t="s">
-        <v>545</v>
+        <v>551</v>
       </c>
     </row>
     <row r="30" spans="5:5">
       <c r="E30" t="s">
-        <v>546</v>
+        <v>552</v>
       </c>
     </row>
     <row r="31" spans="6:6">
       <c r="F31" t="s">
-        <v>547</v>
+        <v>553</v>
       </c>
     </row>
     <row r="32" spans="5:5">
       <c r="E32" t="s">
-        <v>548</v>
+        <v>554</v>
       </c>
     </row>
     <row r="33" spans="4:4">
       <c r="D33" t="s">
-        <v>549</v>
+        <v>555</v>
       </c>
     </row>
     <row r="34" spans="5:5">
       <c r="E34" t="s">
-        <v>550</v>
+        <v>556</v>
       </c>
     </row>
     <row r="35" spans="5:5">
       <c r="E35" t="s">
-        <v>551</v>
+        <v>557</v>
       </c>
     </row>
     <row r="36" spans="6:6">
       <c r="F36" t="s">
-        <v>552</v>
+        <v>558</v>
       </c>
     </row>
   </sheetData>
@@ -7820,247 +7883,247 @@
         <v>20240421</v>
       </c>
       <c r="B2" t="s">
-        <v>553</v>
+        <v>559</v>
       </c>
     </row>
     <row r="3" spans="3:3">
       <c r="C3" t="s">
-        <v>554</v>
+        <v>560</v>
       </c>
     </row>
     <row r="4" spans="3:3">
       <c r="C4" t="s">
-        <v>555</v>
+        <v>561</v>
       </c>
     </row>
     <row r="5" spans="3:3">
       <c r="C5" t="s">
-        <v>556</v>
+        <v>562</v>
       </c>
     </row>
     <row r="6" spans="3:3">
       <c r="C6" t="s">
-        <v>557</v>
+        <v>563</v>
       </c>
     </row>
     <row r="7" spans="2:2">
       <c r="B7" t="s">
-        <v>558</v>
+        <v>564</v>
       </c>
     </row>
     <row r="8" spans="3:3">
       <c r="C8" t="s">
-        <v>559</v>
+        <v>565</v>
       </c>
     </row>
     <row r="9" spans="3:3">
       <c r="C9" t="s">
-        <v>560</v>
+        <v>566</v>
       </c>
     </row>
     <row r="10" spans="3:3">
       <c r="C10" t="s">
-        <v>561</v>
+        <v>567</v>
       </c>
     </row>
     <row r="11" spans="2:2">
       <c r="B11" t="s">
-        <v>562</v>
+        <v>568</v>
       </c>
     </row>
     <row r="12" spans="3:3">
       <c r="C12" t="s">
-        <v>563</v>
+        <v>569</v>
       </c>
     </row>
     <row r="13" spans="3:3">
       <c r="C13" t="s">
-        <v>564</v>
+        <v>570</v>
       </c>
     </row>
     <row r="14" spans="3:3">
       <c r="C14" t="s">
-        <v>565</v>
+        <v>571</v>
       </c>
     </row>
     <row r="15" spans="4:4">
       <c r="D15" t="s">
-        <v>566</v>
+        <v>572</v>
       </c>
     </row>
     <row r="16" spans="4:4">
       <c r="D16" t="s">
-        <v>567</v>
+        <v>573</v>
       </c>
     </row>
     <row r="17" spans="4:4">
       <c r="D17" t="s">
-        <v>568</v>
+        <v>574</v>
       </c>
     </row>
     <row r="18" spans="5:5">
       <c r="E18" t="s">
-        <v>569</v>
+        <v>575</v>
       </c>
     </row>
     <row r="19" spans="4:4">
       <c r="D19" t="s">
-        <v>570</v>
+        <v>576</v>
       </c>
     </row>
     <row r="20" spans="3:3">
       <c r="C20" t="s">
-        <v>571</v>
+        <v>577</v>
       </c>
     </row>
     <row r="21" spans="4:4">
       <c r="D21" t="s">
-        <v>572</v>
+        <v>578</v>
       </c>
     </row>
     <row r="22" spans="4:4">
       <c r="D22" t="s">
-        <v>573</v>
+        <v>579</v>
       </c>
     </row>
     <row r="23" spans="4:4">
       <c r="D23" t="s">
-        <v>574</v>
+        <v>580</v>
       </c>
     </row>
     <row r="24" spans="5:5">
       <c r="E24" t="s">
-        <v>575</v>
+        <v>581</v>
       </c>
     </row>
     <row r="25" spans="3:3">
       <c r="C25" t="s">
-        <v>576</v>
+        <v>582</v>
       </c>
     </row>
     <row r="26" spans="4:4">
       <c r="D26" t="s">
-        <v>572</v>
+        <v>578</v>
       </c>
     </row>
     <row r="27" spans="4:4">
       <c r="D27" t="s">
-        <v>573</v>
+        <v>579</v>
       </c>
     </row>
     <row r="28" spans="4:4">
       <c r="D28" t="s">
-        <v>577</v>
+        <v>583</v>
       </c>
     </row>
     <row r="29" spans="5:5">
       <c r="E29" t="s">
-        <v>578</v>
+        <v>584</v>
       </c>
     </row>
     <row r="30" spans="3:3">
       <c r="C30" t="s">
-        <v>579</v>
+        <v>585</v>
       </c>
     </row>
     <row r="31" spans="4:4">
       <c r="D31" t="s">
-        <v>580</v>
+        <v>586</v>
       </c>
     </row>
     <row r="32" spans="2:2">
       <c r="B32" t="s">
-        <v>581</v>
+        <v>587</v>
       </c>
     </row>
     <row r="33" spans="2:2">
       <c r="B33" t="s">
-        <v>582</v>
+        <v>588</v>
       </c>
     </row>
     <row r="34" spans="3:3">
       <c r="C34" t="s">
-        <v>583</v>
+        <v>589</v>
       </c>
     </row>
     <row r="35" spans="3:3">
       <c r="C35" t="s">
-        <v>584</v>
+        <v>590</v>
       </c>
     </row>
     <row r="36" spans="2:2">
       <c r="B36" t="s">
-        <v>585</v>
+        <v>591</v>
       </c>
     </row>
     <row r="37" spans="3:3">
       <c r="C37" t="s">
-        <v>586</v>
+        <v>592</v>
       </c>
     </row>
     <row r="38" spans="3:3">
       <c r="C38" t="s">
-        <v>587</v>
+        <v>593</v>
       </c>
     </row>
     <row r="39" spans="4:4">
       <c r="D39" t="s">
-        <v>588</v>
+        <v>594</v>
       </c>
     </row>
     <row r="40" spans="4:4">
       <c r="D40" t="s">
-        <v>589</v>
+        <v>595</v>
       </c>
     </row>
     <row r="41" spans="3:3">
       <c r="C41" t="s">
-        <v>590</v>
+        <v>596</v>
       </c>
     </row>
     <row r="42" spans="4:4">
       <c r="D42" t="s">
-        <v>591</v>
+        <v>597</v>
       </c>
     </row>
     <row r="43" spans="4:4">
       <c r="D43" t="s">
-        <v>592</v>
+        <v>598</v>
       </c>
     </row>
     <row r="44" spans="4:4">
       <c r="D44" t="s">
-        <v>593</v>
+        <v>599</v>
       </c>
     </row>
     <row r="45" spans="4:4">
       <c r="D45" t="s">
-        <v>594</v>
+        <v>600</v>
       </c>
     </row>
     <row r="46" spans="5:5">
       <c r="E46" t="s">
-        <v>595</v>
+        <v>601</v>
       </c>
     </row>
     <row r="47" spans="5:5">
       <c r="E47" t="s">
-        <v>596</v>
+        <v>602</v>
       </c>
     </row>
     <row r="48" spans="4:4">
       <c r="D48" t="s">
-        <v>597</v>
+        <v>603</v>
       </c>
     </row>
     <row r="49" spans="4:4">
       <c r="D49" t="s">
-        <v>598</v>
+        <v>604</v>
       </c>
     </row>
     <row r="50" spans="4:4">
       <c r="D50" t="s">
-        <v>599</v>
+        <v>605</v>
       </c>
     </row>
   </sheetData>
@@ -8117,192 +8180,192 @@
         <v>20240422</v>
       </c>
       <c r="B2" t="s">
-        <v>600</v>
+        <v>606</v>
       </c>
     </row>
     <row r="3" spans="3:3">
       <c r="C3" t="s">
-        <v>601</v>
+        <v>607</v>
       </c>
     </row>
     <row r="4" spans="3:3">
       <c r="C4" t="s">
-        <v>602</v>
+        <v>608</v>
       </c>
     </row>
     <row r="5" spans="3:3">
       <c r="C5" t="s">
-        <v>603</v>
+        <v>609</v>
       </c>
     </row>
     <row r="6" spans="3:3">
       <c r="C6" t="s">
-        <v>604</v>
+        <v>610</v>
       </c>
     </row>
     <row r="7" spans="4:4">
       <c r="D7" t="s">
-        <v>605</v>
+        <v>611</v>
       </c>
     </row>
     <row r="8" spans="5:5">
       <c r="E8" t="s">
-        <v>606</v>
+        <v>612</v>
       </c>
     </row>
     <row r="9" spans="5:5">
       <c r="E9" t="s">
-        <v>607</v>
+        <v>613</v>
       </c>
     </row>
     <row r="10" spans="5:5">
       <c r="E10" t="s">
-        <v>608</v>
+        <v>614</v>
       </c>
     </row>
     <row r="11" spans="4:4">
       <c r="D11" t="s">
-        <v>609</v>
+        <v>615</v>
       </c>
     </row>
     <row r="12" spans="5:5">
       <c r="E12" t="s">
-        <v>610</v>
+        <v>616</v>
       </c>
     </row>
     <row r="13" spans="5:5">
       <c r="E13" t="s">
-        <v>611</v>
+        <v>617</v>
       </c>
     </row>
     <row r="14" spans="5:5">
       <c r="E14" t="s">
-        <v>612</v>
+        <v>618</v>
       </c>
     </row>
     <row r="15" spans="3:3">
       <c r="C15" t="s">
-        <v>613</v>
+        <v>619</v>
       </c>
     </row>
     <row r="16" spans="4:4">
       <c r="D16" t="s">
-        <v>614</v>
+        <v>620</v>
       </c>
     </row>
     <row r="17" spans="4:4">
       <c r="D17" t="s">
-        <v>615</v>
+        <v>621</v>
       </c>
     </row>
     <row r="18" spans="4:4">
       <c r="D18" t="s">
-        <v>616</v>
+        <v>622</v>
       </c>
     </row>
     <row r="19" spans="2:2">
       <c r="B19" t="s">
-        <v>617</v>
+        <v>623</v>
       </c>
     </row>
     <row r="20" spans="3:3">
       <c r="C20" t="s">
-        <v>618</v>
+        <v>624</v>
       </c>
     </row>
     <row r="21" spans="3:3">
       <c r="C21" t="s">
-        <v>619</v>
+        <v>625</v>
       </c>
     </row>
     <row r="22" spans="3:3">
       <c r="C22" t="s">
-        <v>620</v>
+        <v>626</v>
       </c>
     </row>
     <row r="23" spans="2:2">
       <c r="B23" t="s">
-        <v>621</v>
+        <v>627</v>
       </c>
     </row>
     <row r="24" spans="3:3">
       <c r="C24" t="s">
-        <v>622</v>
+        <v>628</v>
       </c>
     </row>
     <row r="25" spans="4:4">
       <c r="D25" t="s">
-        <v>623</v>
+        <v>629</v>
       </c>
     </row>
     <row r="26" spans="4:4">
       <c r="D26" t="s">
-        <v>624</v>
+        <v>630</v>
       </c>
     </row>
     <row r="27" spans="3:3">
       <c r="C27" t="s">
-        <v>625</v>
+        <v>631</v>
       </c>
     </row>
     <row r="28" spans="2:2">
       <c r="B28" t="s">
-        <v>626</v>
+        <v>632</v>
       </c>
     </row>
     <row r="29" spans="2:2">
       <c r="B29" t="s">
-        <v>627</v>
+        <v>633</v>
       </c>
     </row>
     <row r="30" spans="3:3">
       <c r="C30" t="s">
-        <v>628</v>
+        <v>634</v>
       </c>
     </row>
     <row r="31" spans="3:3">
       <c r="C31" t="s">
-        <v>629</v>
+        <v>635</v>
       </c>
     </row>
     <row r="32" spans="4:4">
       <c r="D32" t="s">
-        <v>630</v>
+        <v>636</v>
       </c>
     </row>
     <row r="33" spans="4:4">
       <c r="D33" t="s">
-        <v>631</v>
+        <v>637</v>
       </c>
     </row>
     <row r="34" spans="4:4">
       <c r="D34" t="s">
-        <v>632</v>
+        <v>638</v>
       </c>
     </row>
     <row r="35" spans="3:3">
       <c r="C35" t="s">
-        <v>633</v>
+        <v>639</v>
       </c>
     </row>
     <row r="36" spans="2:2">
       <c r="B36" t="s">
-        <v>634</v>
+        <v>640</v>
       </c>
     </row>
     <row r="37" spans="3:3">
       <c r="C37" t="s">
-        <v>635</v>
+        <v>641</v>
       </c>
     </row>
     <row r="38" spans="3:3">
       <c r="C38" t="s">
-        <v>636</v>
+        <v>642</v>
       </c>
     </row>
     <row r="39" spans="3:3">
       <c r="C39" t="s">
-        <v>637</v>
+        <v>643</v>
       </c>
     </row>
   </sheetData>
@@ -8359,142 +8422,142 @@
         <v>20240423</v>
       </c>
       <c r="B2" t="s">
-        <v>638</v>
+        <v>644</v>
       </c>
     </row>
     <row r="3" spans="3:3">
       <c r="C3" t="s">
-        <v>639</v>
+        <v>645</v>
       </c>
     </row>
     <row r="4" spans="4:4">
       <c r="D4" t="s">
-        <v>640</v>
+        <v>646</v>
       </c>
     </row>
     <row r="5" spans="3:3">
       <c r="C5" t="s">
-        <v>641</v>
+        <v>647</v>
       </c>
     </row>
     <row r="6" spans="4:4">
       <c r="D6" t="s">
-        <v>642</v>
+        <v>648</v>
       </c>
     </row>
     <row r="7" spans="2:2">
       <c r="B7" t="s">
-        <v>643</v>
+        <v>649</v>
       </c>
     </row>
     <row r="8" spans="3:3">
       <c r="C8" t="s">
-        <v>644</v>
+        <v>650</v>
       </c>
     </row>
     <row r="9" spans="3:3">
       <c r="C9" t="s">
-        <v>645</v>
+        <v>651</v>
       </c>
     </row>
     <row r="10" spans="4:4">
       <c r="D10" t="s">
-        <v>646</v>
+        <v>652</v>
       </c>
     </row>
     <row r="11" spans="4:4">
       <c r="D11" t="s">
-        <v>647</v>
+        <v>653</v>
       </c>
     </row>
     <row r="12" spans="5:5">
       <c r="E12" t="s">
-        <v>648</v>
+        <v>654</v>
       </c>
     </row>
     <row r="13" spans="5:5">
       <c r="E13" t="s">
-        <v>649</v>
+        <v>655</v>
       </c>
     </row>
     <row r="14" spans="6:6">
       <c r="F14" t="s">
-        <v>650</v>
+        <v>656</v>
       </c>
     </row>
     <row r="15" spans="6:6">
       <c r="F15" t="s">
-        <v>651</v>
+        <v>657</v>
       </c>
     </row>
     <row r="16" spans="7:7">
       <c r="G16" t="s">
-        <v>652</v>
+        <v>658</v>
       </c>
     </row>
     <row r="17" spans="2:2">
       <c r="B17" t="s">
-        <v>653</v>
+        <v>659</v>
       </c>
     </row>
     <row r="18" spans="3:3">
       <c r="C18" t="s">
-        <v>654</v>
+        <v>660</v>
       </c>
     </row>
     <row r="19" spans="3:3">
       <c r="C19" t="s">
-        <v>655</v>
+        <v>661</v>
       </c>
     </row>
     <row r="20" spans="4:4">
       <c r="D20" t="s">
-        <v>656</v>
+        <v>662</v>
       </c>
     </row>
     <row r="21" spans="4:4">
       <c r="D21" t="s">
-        <v>657</v>
+        <v>663</v>
       </c>
     </row>
     <row r="22" spans="5:5">
       <c r="E22" t="s">
-        <v>658</v>
+        <v>664</v>
       </c>
     </row>
     <row r="23" spans="5:5">
       <c r="E23" t="s">
-        <v>659</v>
+        <v>665</v>
       </c>
     </row>
     <row r="24" spans="5:5">
       <c r="E24" t="s">
-        <v>660</v>
+        <v>666</v>
       </c>
     </row>
     <row r="25" spans="4:4">
       <c r="D25" t="s">
-        <v>661</v>
+        <v>667</v>
       </c>
     </row>
     <row r="26" spans="5:5">
       <c r="E26" t="s">
-        <v>662</v>
+        <v>668</v>
       </c>
     </row>
     <row r="27" spans="6:6">
       <c r="F27" t="s">
-        <v>663</v>
+        <v>669</v>
       </c>
     </row>
     <row r="28" spans="5:5">
       <c r="E28" t="s">
-        <v>664</v>
+        <v>670</v>
       </c>
     </row>
     <row r="29" spans="6:6">
       <c r="F29" t="s">
-        <v>665</v>
+        <v>671</v>
       </c>
     </row>
   </sheetData>
@@ -8551,122 +8614,122 @@
         <v>20240424</v>
       </c>
       <c r="B2" t="s">
-        <v>666</v>
+        <v>672</v>
       </c>
     </row>
     <row r="3" spans="2:2">
       <c r="B3" t="s">
-        <v>667</v>
+        <v>673</v>
       </c>
     </row>
     <row r="4" spans="3:3">
       <c r="C4" t="s">
-        <v>668</v>
+        <v>674</v>
       </c>
     </row>
     <row r="5" spans="3:3">
       <c r="C5" t="s">
-        <v>669</v>
+        <v>675</v>
       </c>
     </row>
     <row r="6" spans="2:2">
       <c r="B6" t="s">
-        <v>670</v>
+        <v>676</v>
       </c>
     </row>
     <row r="7" spans="3:3">
       <c r="C7" t="s">
-        <v>671</v>
+        <v>677</v>
       </c>
     </row>
     <row r="8" spans="4:4">
       <c r="D8" t="s">
-        <v>672</v>
+        <v>678</v>
       </c>
     </row>
     <row r="9" spans="4:4">
       <c r="D9" t="s">
-        <v>673</v>
+        <v>679</v>
       </c>
     </row>
     <row r="10" spans="4:4">
       <c r="D10" t="s">
-        <v>674</v>
+        <v>680</v>
       </c>
     </row>
     <row r="11" spans="4:4">
       <c r="D11" t="s">
-        <v>675</v>
+        <v>681</v>
       </c>
     </row>
     <row r="12" spans="4:4">
       <c r="D12" t="s">
-        <v>676</v>
+        <v>682</v>
       </c>
     </row>
     <row r="13" spans="3:3">
       <c r="C13" t="s">
-        <v>677</v>
+        <v>683</v>
       </c>
     </row>
     <row r="14" spans="4:4">
       <c r="D14" t="s">
-        <v>678</v>
+        <v>684</v>
       </c>
     </row>
     <row r="15" spans="4:4">
       <c r="D15" t="s">
-        <v>679</v>
+        <v>685</v>
       </c>
     </row>
     <row r="16" spans="4:4">
       <c r="D16" t="s">
-        <v>680</v>
+        <v>686</v>
       </c>
     </row>
     <row r="17" spans="4:4">
       <c r="D17" t="s">
-        <v>681</v>
+        <v>687</v>
       </c>
     </row>
     <row r="18" spans="3:3">
       <c r="C18" t="s">
-        <v>682</v>
+        <v>688</v>
       </c>
     </row>
     <row r="19" spans="4:4">
       <c r="D19" t="s">
-        <v>683</v>
+        <v>689</v>
       </c>
     </row>
     <row r="20" spans="4:4">
       <c r="D20" t="s">
-        <v>684</v>
+        <v>690</v>
       </c>
     </row>
     <row r="21" spans="5:5">
       <c r="E21" t="s">
-        <v>685</v>
+        <v>691</v>
       </c>
     </row>
     <row r="22" spans="5:5">
       <c r="E22" t="s">
-        <v>686</v>
+        <v>692</v>
       </c>
     </row>
     <row r="23" spans="5:5">
       <c r="E23" t="s">
-        <v>687</v>
+        <v>693</v>
       </c>
     </row>
     <row r="24" spans="5:5">
       <c r="E24" t="s">
-        <v>688</v>
+        <v>694</v>
       </c>
     </row>
     <row r="25" spans="3:3">
       <c r="C25" t="s">
-        <v>689</v>
+        <v>695</v>
       </c>
     </row>
   </sheetData>
@@ -8678,7 +8741,7 @@
 <file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H81"/>
+  <dimension ref="A1:H75"/>
   <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="1" width="9.66666666666667"/>
@@ -8687,15 +8750,15 @@
     <row r="1" s="1" customFormat="1" spans="1:8">
       <c r="A1" s="1">
         <f>SUM(B1:AZ1)</f>
-        <v>24.1666666666667</v>
+        <v>22</v>
       </c>
       <c r="B1" s="1">
-        <f t="shared" ref="B1:H1" si="0">COUNTA(B2:B2055)/COLUMN()</f>
-        <v>3.5</v>
+        <f t="shared" ref="B1:H1" si="0">COUNTA(B2:B2049)/COLUMN()</f>
+        <v>3</v>
       </c>
       <c r="C1" s="1">
         <f t="shared" si="0"/>
-        <v>12</v>
+        <v>10.3333333333333</v>
       </c>
       <c r="D1" s="1">
         <f t="shared" si="0"/>
@@ -8723,402 +8786,372 @@
         <v>20240425</v>
       </c>
       <c r="B2" t="s">
-        <v>690</v>
+        <v>696</v>
       </c>
     </row>
     <row r="3" spans="3:3">
       <c r="C3" t="s">
-        <v>691</v>
+        <v>697</v>
       </c>
     </row>
     <row r="4" spans="3:3">
       <c r="C4" t="s">
-        <v>692</v>
+        <v>698</v>
       </c>
     </row>
     <row r="5" spans="3:3">
       <c r="C5" t="s">
-        <v>693</v>
+        <v>699</v>
       </c>
     </row>
     <row r="6" spans="3:3">
       <c r="C6" t="s">
-        <v>694</v>
+        <v>700</v>
       </c>
     </row>
     <row r="7" spans="3:3">
       <c r="C7" t="s">
-        <v>695</v>
+        <v>701</v>
       </c>
     </row>
     <row r="8" spans="3:3">
       <c r="C8" t="s">
-        <v>696</v>
+        <v>702</v>
       </c>
     </row>
     <row r="9" spans="2:2">
       <c r="B9" t="s">
-        <v>1</v>
+        <v>703</v>
       </c>
     </row>
     <row r="10" spans="3:3">
       <c r="C10" t="s">
-        <v>697</v>
+        <v>704</v>
       </c>
     </row>
     <row r="11" spans="3:3">
       <c r="C11" t="s">
-        <v>698</v>
+        <v>705</v>
       </c>
     </row>
     <row r="12" spans="3:3">
       <c r="C12" t="s">
-        <v>699</v>
-      </c>
-    </row>
-    <row r="13" spans="3:3">
-      <c r="C13" t="s">
-        <v>700</v>
-      </c>
-    </row>
-    <row r="14" spans="3:3">
-      <c r="C14" t="s">
-        <v>701</v>
-      </c>
-    </row>
-    <row r="15" spans="2:2">
-      <c r="B15" t="s">
-        <v>702</v>
+        <v>706</v>
+      </c>
+    </row>
+    <row r="13" spans="4:4">
+      <c r="D13" t="s">
+        <v>707</v>
+      </c>
+    </row>
+    <row r="14" spans="4:4">
+      <c r="D14" t="s">
+        <v>708</v>
+      </c>
+    </row>
+    <row r="15" spans="4:4">
+      <c r="D15" t="s">
+        <v>709</v>
       </c>
     </row>
     <row r="16" spans="3:3">
       <c r="C16" t="s">
-        <v>703</v>
-      </c>
-    </row>
-    <row r="17" spans="3:3">
-      <c r="C17" t="s">
-        <v>704</v>
-      </c>
-    </row>
-    <row r="18" spans="3:3">
-      <c r="C18" t="s">
-        <v>705</v>
+        <v>710</v>
+      </c>
+    </row>
+    <row r="17" spans="4:4">
+      <c r="D17" t="s">
+        <v>711</v>
+      </c>
+    </row>
+    <row r="18" spans="4:4">
+      <c r="D18" t="s">
+        <v>712</v>
       </c>
     </row>
     <row r="19" spans="4:4">
       <c r="D19" t="s">
-        <v>706</v>
-      </c>
-    </row>
-    <row r="20" spans="4:4">
-      <c r="D20" t="s">
-        <v>707</v>
+        <v>713</v>
+      </c>
+    </row>
+    <row r="20" spans="3:3">
+      <c r="C20" t="s">
+        <v>714</v>
       </c>
     </row>
     <row r="21" spans="4:4">
       <c r="D21" t="s">
-        <v>708</v>
-      </c>
-    </row>
-    <row r="22" spans="3:3">
-      <c r="C22" t="s">
-        <v>709</v>
+        <v>715</v>
+      </c>
+    </row>
+    <row r="22" spans="4:4">
+      <c r="D22" t="s">
+        <v>716</v>
       </c>
     </row>
     <row r="23" spans="4:4">
       <c r="D23" t="s">
-        <v>710</v>
+        <v>717</v>
       </c>
     </row>
     <row r="24" spans="4:4">
       <c r="D24" t="s">
-        <v>711</v>
-      </c>
-    </row>
-    <row r="25" spans="4:4">
-      <c r="D25" t="s">
-        <v>712</v>
-      </c>
-    </row>
-    <row r="26" spans="3:3">
-      <c r="C26" t="s">
-        <v>713</v>
+        <v>718</v>
+      </c>
+    </row>
+    <row r="25" spans="3:3">
+      <c r="C25" t="s">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="26" spans="4:4">
+      <c r="D26" t="s">
+        <v>720</v>
       </c>
     </row>
     <row r="27" spans="4:4">
       <c r="D27" t="s">
-        <v>714</v>
+        <v>721</v>
       </c>
     </row>
     <row r="28" spans="4:4">
       <c r="D28" t="s">
-        <v>715</v>
-      </c>
-    </row>
-    <row r="29" spans="4:4">
-      <c r="D29" t="s">
-        <v>716</v>
-      </c>
-    </row>
-    <row r="30" spans="4:4">
-      <c r="D30" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="31" spans="3:3">
-      <c r="C31" t="s">
-        <v>718</v>
+        <v>722</v>
+      </c>
+    </row>
+    <row r="29" spans="5:5">
+      <c r="E29" t="s">
+        <v>723</v>
+      </c>
+    </row>
+    <row r="30" spans="3:3">
+      <c r="C30" t="s">
+        <v>724</v>
+      </c>
+    </row>
+    <row r="31" spans="4:4">
+      <c r="D31" t="s">
+        <v>725</v>
       </c>
     </row>
     <row r="32" spans="4:4">
       <c r="D32" t="s">
-        <v>719</v>
+        <v>726</v>
       </c>
     </row>
     <row r="33" spans="4:4">
       <c r="D33" t="s">
-        <v>720</v>
-      </c>
-    </row>
-    <row r="34" spans="4:4">
-      <c r="D34" t="s">
+        <v>727</v>
+      </c>
+    </row>
+    <row r="34" spans="3:3">
+      <c r="C34" t="s">
+        <v>728</v>
+      </c>
+    </row>
+    <row r="35" spans="4:4">
+      <c r="D35" t="s">
+        <v>729</v>
+      </c>
+    </row>
+    <row r="36" spans="4:4">
+      <c r="D36" t="s">
         <v>721</v>
-      </c>
-    </row>
-    <row r="35" spans="5:5">
-      <c r="E35" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="36" spans="3:3">
-      <c r="C36" t="s">
-        <v>723</v>
       </c>
     </row>
     <row r="37" spans="4:4">
       <c r="D37" t="s">
-        <v>724</v>
-      </c>
-    </row>
-    <row r="38" spans="4:4">
-      <c r="D38" t="s">
-        <v>725</v>
-      </c>
-    </row>
-    <row r="39" spans="4:4">
-      <c r="D39" t="s">
-        <v>726</v>
-      </c>
-    </row>
-    <row r="40" spans="3:3">
-      <c r="C40" t="s">
-        <v>727</v>
-      </c>
-    </row>
-    <row r="41" spans="4:4">
-      <c r="D41" t="s">
-        <v>728</v>
-      </c>
-    </row>
-    <row r="42" spans="4:4">
-      <c r="D42" t="s">
-        <v>720</v>
-      </c>
-    </row>
-    <row r="43" spans="4:4">
-      <c r="D43" t="s">
-        <v>729</v>
-      </c>
-    </row>
-    <row r="44" spans="5:5">
-      <c r="E44" t="s">
         <v>730</v>
+      </c>
+    </row>
+    <row r="38" spans="5:5">
+      <c r="E38" t="s">
+        <v>731</v>
+      </c>
+    </row>
+    <row r="39" spans="5:5">
+      <c r="E39" t="s">
+        <v>732</v>
+      </c>
+    </row>
+    <row r="40" spans="5:5">
+      <c r="E40" t="s">
+        <v>733</v>
+      </c>
+    </row>
+    <row r="41" spans="6:6">
+      <c r="F41" t="s">
+        <v>734</v>
+      </c>
+    </row>
+    <row r="42" spans="6:6">
+      <c r="F42" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="43" spans="6:6">
+      <c r="F43" t="s">
+        <v>736</v>
+      </c>
+    </row>
+    <row r="44" spans="6:6">
+      <c r="F44" t="s">
+        <v>737</v>
       </c>
     </row>
     <row r="45" spans="5:5">
       <c r="E45" t="s">
-        <v>731</v>
-      </c>
-    </row>
-    <row r="46" spans="5:5">
-      <c r="E46" t="s">
-        <v>732</v>
-      </c>
-    </row>
-    <row r="47" spans="6:6">
-      <c r="F47" t="s">
-        <v>733</v>
-      </c>
-    </row>
-    <row r="48" spans="6:6">
-      <c r="F48" t="s">
-        <v>734</v>
-      </c>
-    </row>
-    <row r="49" spans="6:6">
-      <c r="F49" t="s">
-        <v>735</v>
-      </c>
-    </row>
-    <row r="50" spans="6:6">
-      <c r="F50" t="s">
-        <v>736</v>
-      </c>
-    </row>
-    <row r="51" spans="5:5">
-      <c r="E51" t="s">
-        <v>737</v>
-      </c>
-    </row>
-    <row r="52" spans="2:2">
-      <c r="B52" t="s">
         <v>738</v>
+      </c>
+    </row>
+    <row r="46" spans="2:2">
+      <c r="B46" t="s">
+        <v>739</v>
+      </c>
+    </row>
+    <row r="47" spans="3:3">
+      <c r="C47" t="s">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="48" spans="3:3">
+      <c r="C48" t="s">
+        <v>741</v>
+      </c>
+    </row>
+    <row r="49" spans="4:4">
+      <c r="D49" t="s">
+        <v>742</v>
+      </c>
+    </row>
+    <row r="50" spans="4:4">
+      <c r="D50" t="s">
+        <v>743</v>
+      </c>
+    </row>
+    <row r="51" spans="4:4">
+      <c r="D51" t="s">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="52" spans="3:3">
+      <c r="C52" t="s">
+        <v>745</v>
       </c>
     </row>
     <row r="53" spans="3:3">
       <c r="C53" t="s">
-        <v>739</v>
-      </c>
-    </row>
-    <row r="54" spans="3:3">
-      <c r="C54" t="s">
-        <v>740</v>
+        <v>746</v>
+      </c>
+    </row>
+    <row r="54" spans="4:4">
+      <c r="D54" t="s">
+        <v>747</v>
       </c>
     </row>
     <row r="55" spans="4:4">
       <c r="D55" t="s">
-        <v>741</v>
+        <v>748</v>
       </c>
     </row>
     <row r="56" spans="4:4">
       <c r="D56" t="s">
-        <v>742</v>
+        <v>749</v>
       </c>
     </row>
     <row r="57" spans="4:4">
       <c r="D57" t="s">
-        <v>743</v>
-      </c>
-    </row>
-    <row r="58" spans="3:3">
-      <c r="C58" t="s">
-        <v>744</v>
+        <v>750</v>
+      </c>
+    </row>
+    <row r="58" spans="2:2">
+      <c r="B58" t="s">
+        <v>751</v>
       </c>
     </row>
     <row r="59" spans="3:3">
       <c r="C59" t="s">
-        <v>745</v>
-      </c>
-    </row>
-    <row r="60" spans="4:4">
-      <c r="D60" t="s">
-        <v>746</v>
-      </c>
-    </row>
-    <row r="61" spans="4:4">
-      <c r="D61" t="s">
-        <v>747</v>
-      </c>
-    </row>
-    <row r="62" spans="4:4">
-      <c r="D62" t="s">
-        <v>748</v>
-      </c>
-    </row>
-    <row r="63" spans="4:4">
-      <c r="D63" t="s">
-        <v>749</v>
-      </c>
-    </row>
-    <row r="64" spans="2:2">
-      <c r="B64" t="s">
-        <v>750</v>
+        <v>752</v>
+      </c>
+    </row>
+    <row r="60" spans="3:3">
+      <c r="C60" t="s">
+        <v>753</v>
+      </c>
+    </row>
+    <row r="61" spans="3:3">
+      <c r="C61" t="s">
+        <v>754</v>
+      </c>
+    </row>
+    <row r="62" spans="3:3">
+      <c r="C62" t="s">
+        <v>755</v>
+      </c>
+    </row>
+    <row r="63" spans="3:3">
+      <c r="C63" t="s">
+        <v>756</v>
+      </c>
+    </row>
+    <row r="64" spans="3:3">
+      <c r="C64" t="s">
+        <v>757</v>
       </c>
     </row>
     <row r="65" spans="3:3">
       <c r="C65" t="s">
-        <v>751</v>
-      </c>
-    </row>
-    <row r="66" spans="3:3">
-      <c r="C66" t="s">
-        <v>752</v>
+        <v>758</v>
+      </c>
+    </row>
+    <row r="66" spans="2:2">
+      <c r="B66" t="s">
+        <v>759</v>
       </c>
     </row>
     <row r="67" spans="3:3">
       <c r="C67" t="s">
-        <v>753</v>
+        <v>760</v>
       </c>
     </row>
     <row r="68" spans="3:3">
       <c r="C68" t="s">
-        <v>754</v>
+        <v>761</v>
       </c>
     </row>
     <row r="69" spans="3:3">
       <c r="C69" t="s">
-        <v>755</v>
-      </c>
-    </row>
-    <row r="70" spans="3:3">
-      <c r="C70" t="s">
-        <v>756</v>
-      </c>
-    </row>
-    <row r="71" spans="3:3">
-      <c r="C71" t="s">
-        <v>757</v>
+        <v>762</v>
+      </c>
+    </row>
+    <row r="70" spans="4:4">
+      <c r="D70" t="s">
+        <v>763</v>
+      </c>
+    </row>
+    <row r="71" spans="4:4">
+      <c r="D71" t="s">
+        <v>764</v>
       </c>
     </row>
     <row r="72" spans="2:2">
-      <c r="B72" t="s">
-        <v>758</v>
+      <c r="B72" s="3" t="s">
+        <v>765</v>
       </c>
     </row>
     <row r="73" spans="3:3">
       <c r="C73" t="s">
-        <v>759</v>
+        <v>766</v>
       </c>
     </row>
     <row r="74" spans="3:3">
       <c r="C74" t="s">
-        <v>760</v>
+        <v>767</v>
       </c>
     </row>
     <row r="75" spans="3:3">
       <c r="C75" t="s">
-        <v>761</v>
-      </c>
-    </row>
-    <row r="76" spans="4:4">
-      <c r="D76" t="s">
-        <v>762</v>
-      </c>
-    </row>
-    <row r="77" spans="4:4">
-      <c r="D77" t="s">
-        <v>763</v>
-      </c>
-    </row>
-    <row r="78" spans="2:2">
-      <c r="B78" s="3" t="s">
-        <v>764</v>
-      </c>
-    </row>
-    <row r="79" spans="3:3">
-      <c r="C79" t="s">
-        <v>765</v>
-      </c>
-    </row>
-    <row r="80" spans="3:3">
-      <c r="C80" t="s">
-        <v>766</v>
-      </c>
-    </row>
-    <row r="81" spans="3:3">
-      <c r="C81" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
     </row>
   </sheetData>
@@ -9175,733 +9208,820 @@
         <v>20240426</v>
       </c>
       <c r="B2" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
     </row>
     <row r="3" spans="3:3">
       <c r="C3" s="2" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
     </row>
     <row r="4" spans="3:3">
       <c r="C4" s="2" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
     </row>
     <row r="5" spans="3:3">
       <c r="C5" s="2" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
     </row>
     <row r="6" spans="3:3">
       <c r="C6" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
     </row>
     <row r="7" spans="2:2">
       <c r="B7" t="s">
-        <v>773</v>
+        <v>774</v>
       </c>
     </row>
     <row r="8" spans="3:3">
       <c r="C8" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
     </row>
     <row r="9" spans="3:3">
       <c r="C9" t="s">
-        <v>775</v>
+        <v>776</v>
       </c>
     </row>
     <row r="10" spans="3:3">
       <c r="C10" s="2" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
     </row>
     <row r="11" spans="3:3">
       <c r="C11" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
     </row>
     <row r="12" spans="2:2">
       <c r="B12" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
     </row>
     <row r="13" spans="3:3">
       <c r="C13" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
     </row>
     <row r="14" spans="3:3">
       <c r="C14" s="2" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
     </row>
     <row r="15" spans="3:3">
       <c r="C15" s="2" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
     </row>
     <row r="16" spans="3:3">
       <c r="C16" s="2" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
     </row>
     <row r="17" spans="2:3">
       <c r="B17" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="C17" s="2"/>
     </row>
     <row r="18" spans="3:3">
       <c r="C18" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
     </row>
     <row r="19" spans="3:3">
       <c r="C19" s="2" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
     </row>
     <row r="20" spans="3:3">
       <c r="C20" t="s">
-        <v>786</v>
+        <v>787</v>
       </c>
     </row>
     <row r="21" spans="3:3">
       <c r="C21" s="2" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
     </row>
     <row r="22" spans="2:2">
       <c r="B22" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
     </row>
     <row r="23" spans="3:3">
       <c r="C23" t="s">
-        <v>789</v>
+        <v>790</v>
       </c>
     </row>
     <row r="24" spans="3:3">
       <c r="C24" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
     </row>
     <row r="25" spans="3:3">
       <c r="C25" t="s">
-        <v>791</v>
+        <v>792</v>
       </c>
     </row>
     <row r="26" spans="4:4">
       <c r="D26" t="s">
-        <v>792</v>
+        <v>793</v>
       </c>
     </row>
     <row r="27" spans="4:4">
       <c r="D27" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
     </row>
     <row r="28" spans="3:3">
       <c r="C28" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
     </row>
     <row r="29" spans="2:2">
       <c r="B29" t="s">
-        <v>795</v>
+        <v>796</v>
       </c>
     </row>
     <row r="30" spans="3:3">
       <c r="C30" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
     </row>
     <row r="31" spans="4:4">
       <c r="D31" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
     </row>
     <row r="32" spans="4:4">
       <c r="D32" t="s">
-        <v>798</v>
+        <v>799</v>
       </c>
     </row>
     <row r="33" spans="4:4">
       <c r="D33" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
     </row>
     <row r="34" spans="3:3">
       <c r="C34" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
     </row>
     <row r="35" spans="4:4">
       <c r="D35" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
     </row>
     <row r="36" spans="4:4">
       <c r="D36" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
     </row>
     <row r="37" spans="3:3">
       <c r="C37" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
     </row>
     <row r="38" spans="3:3">
       <c r="C38" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="39" spans="2:2">
       <c r="B39" t="s">
-        <v>805</v>
+        <v>806</v>
       </c>
     </row>
     <row r="40" spans="3:3">
       <c r="C40" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
     </row>
     <row r="41" spans="4:4">
       <c r="D41" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
     </row>
     <row r="42" spans="3:3">
       <c r="C42" t="s">
-        <v>808</v>
+        <v>809</v>
       </c>
     </row>
     <row r="43" spans="4:4">
       <c r="D43" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
     </row>
     <row r="44" spans="3:3">
       <c r="C44" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
     </row>
     <row r="45" spans="3:3">
       <c r="C45" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
     </row>
     <row r="46" spans="2:2">
       <c r="B46" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
     </row>
     <row r="47" spans="3:3">
       <c r="C47" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
     </row>
     <row r="48" spans="3:3">
       <c r="C48" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
     </row>
     <row r="49" spans="3:3">
       <c r="C49" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
     </row>
     <row r="50" spans="3:3">
       <c r="C50" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
     </row>
     <row r="51" spans="2:2">
       <c r="B51" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
     </row>
     <row r="52" spans="3:3">
       <c r="C52" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
     </row>
     <row r="53" spans="4:4">
       <c r="D53" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
     </row>
     <row r="54" spans="4:4">
       <c r="D54" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
     </row>
     <row r="55" spans="4:4">
       <c r="D55" t="s">
-        <v>821</v>
+        <v>822</v>
       </c>
     </row>
     <row r="56" spans="3:3">
       <c r="C56" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
     </row>
     <row r="57" spans="3:3">
       <c r="C57" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
     </row>
     <row r="58" spans="4:4">
       <c r="D58" t="s">
-        <v>824</v>
+        <v>825</v>
       </c>
     </row>
     <row r="59" spans="3:3">
       <c r="C59" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
     </row>
     <row r="60" spans="2:2">
       <c r="B60" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
     </row>
     <row r="61" spans="3:3">
       <c r="C61" t="s">
-        <v>827</v>
+        <v>828</v>
       </c>
     </row>
     <row r="62" spans="4:4">
       <c r="D62" t="s">
-        <v>828</v>
+        <v>829</v>
       </c>
     </row>
     <row r="63" spans="5:5">
       <c r="E63" t="s">
-        <v>829</v>
+        <v>830</v>
       </c>
     </row>
     <row r="64" spans="5:5">
       <c r="E64" t="s">
-        <v>830</v>
+        <v>831</v>
       </c>
     </row>
     <row r="65" spans="4:4">
       <c r="D65" t="s">
-        <v>831</v>
+        <v>832</v>
       </c>
     </row>
     <row r="66" spans="5:5">
       <c r="E66" t="s">
-        <v>832</v>
+        <v>833</v>
       </c>
     </row>
     <row r="67" spans="5:5">
       <c r="E67" t="s">
-        <v>833</v>
+        <v>834</v>
       </c>
     </row>
     <row r="68" spans="3:3">
       <c r="C68" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
     </row>
     <row r="69" spans="3:3">
       <c r="C69" t="s">
-        <v>835</v>
+        <v>836</v>
       </c>
     </row>
     <row r="70" spans="3:3">
       <c r="C70" t="s">
-        <v>836</v>
+        <v>837</v>
       </c>
     </row>
     <row r="71" spans="2:2">
       <c r="B71" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
     </row>
     <row r="72" spans="3:3">
       <c r="C72" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
     </row>
     <row r="73" spans="3:3">
       <c r="C73" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
     </row>
     <row r="74" spans="4:4">
       <c r="D74" t="s">
-        <v>840</v>
+        <v>841</v>
       </c>
     </row>
     <row r="75" spans="4:4">
       <c r="D75" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
     </row>
     <row r="76" spans="4:4">
       <c r="D76" t="s">
-        <v>842</v>
+        <v>843</v>
       </c>
     </row>
     <row r="77" spans="3:3">
       <c r="C77" t="s">
-        <v>843</v>
+        <v>844</v>
       </c>
     </row>
     <row r="78" spans="2:2">
       <c r="B78" t="s">
-        <v>844</v>
+        <v>845</v>
       </c>
     </row>
     <row r="79" spans="3:3">
       <c r="C79" s="2" t="s">
-        <v>845</v>
+        <v>846</v>
       </c>
     </row>
     <row r="80" spans="3:3">
       <c r="C80" s="2" t="s">
-        <v>846</v>
+        <v>847</v>
       </c>
     </row>
     <row r="81" spans="3:3">
       <c r="C81" s="2" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
     </row>
     <row r="82" spans="3:3">
       <c r="C82" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
     </row>
     <row r="83" spans="4:4">
       <c r="D83" s="2" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
     </row>
     <row r="84" spans="4:4">
       <c r="D84" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
     </row>
     <row r="85" spans="4:4">
       <c r="D85" t="s">
-        <v>851</v>
+        <v>852</v>
       </c>
     </row>
     <row r="86" spans="4:4">
       <c r="D86" t="s">
-        <v>852</v>
+        <v>853</v>
       </c>
     </row>
     <row r="87" spans="4:4">
       <c r="D87" t="s">
-        <v>853</v>
+        <v>854</v>
       </c>
     </row>
     <row r="88" spans="3:3">
       <c r="C88" t="s">
-        <v>854</v>
+        <v>855</v>
       </c>
     </row>
     <row r="89" spans="3:3">
       <c r="C89" t="s">
-        <v>855</v>
+        <v>856</v>
       </c>
     </row>
     <row r="90" spans="3:3">
       <c r="C90" t="s">
-        <v>856</v>
+        <v>857</v>
       </c>
     </row>
     <row r="91" spans="4:4">
       <c r="D91" t="s">
-        <v>857</v>
+        <v>858</v>
       </c>
     </row>
     <row r="92" spans="4:4">
       <c r="D92" t="s">
-        <v>858</v>
+        <v>859</v>
       </c>
     </row>
     <row r="93" spans="4:4">
       <c r="D93" t="s">
-        <v>859</v>
+        <v>860</v>
       </c>
     </row>
     <row r="94" spans="4:4">
       <c r="D94" t="s">
-        <v>860</v>
+        <v>861</v>
       </c>
     </row>
     <row r="95" spans="2:2">
       <c r="B95" t="s">
-        <v>861</v>
+        <v>862</v>
       </c>
     </row>
     <row r="96" spans="3:3">
       <c r="C96" t="s">
-        <v>862</v>
+        <v>863</v>
       </c>
     </row>
     <row r="97" spans="4:4">
       <c r="D97" t="s">
-        <v>863</v>
+        <v>864</v>
       </c>
     </row>
     <row r="98" spans="4:4">
       <c r="D98" t="s">
-        <v>864</v>
+        <v>865</v>
       </c>
     </row>
     <row r="99" spans="2:2">
       <c r="B99" t="s">
-        <v>865</v>
+        <v>866</v>
       </c>
     </row>
     <row r="100" spans="3:3">
       <c r="C100" t="s">
-        <v>866</v>
+        <v>867</v>
       </c>
     </row>
     <row r="101" spans="4:4">
       <c r="D101" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
     </row>
     <row r="102" spans="4:4">
       <c r="D102" t="s">
-        <v>868</v>
+        <v>869</v>
       </c>
     </row>
     <row r="103" spans="4:4">
       <c r="D103" t="s">
-        <v>869</v>
+        <v>870</v>
       </c>
     </row>
     <row r="104" spans="4:4">
       <c r="D104" t="s">
-        <v>870</v>
+        <v>871</v>
       </c>
     </row>
     <row r="105" spans="4:4">
       <c r="D105" t="s">
-        <v>871</v>
+        <v>872</v>
       </c>
     </row>
     <row r="106" spans="3:3">
       <c r="C106" t="s">
-        <v>872</v>
+        <v>873</v>
       </c>
     </row>
     <row r="107" spans="4:4">
       <c r="D107" t="s">
-        <v>873</v>
+        <v>874</v>
       </c>
     </row>
     <row r="108" spans="4:4">
       <c r="D108" t="s">
-        <v>874</v>
+        <v>875</v>
       </c>
     </row>
     <row r="109" spans="4:4">
       <c r="D109" t="s">
-        <v>875</v>
+        <v>876</v>
       </c>
     </row>
     <row r="110" spans="3:3">
       <c r="C110" t="s">
-        <v>876</v>
+        <v>877</v>
       </c>
     </row>
     <row r="111" spans="4:4">
       <c r="D111" t="s">
-        <v>877</v>
+        <v>878</v>
       </c>
     </row>
     <row r="112" spans="4:4">
       <c r="D112" t="s">
-        <v>878</v>
+        <v>879</v>
       </c>
     </row>
     <row r="113" spans="4:4">
       <c r="D113" t="s">
-        <v>879</v>
+        <v>880</v>
       </c>
     </row>
     <row r="114" spans="4:4">
       <c r="D114" t="s">
-        <v>880</v>
+        <v>881</v>
       </c>
     </row>
     <row r="115" spans="4:4">
       <c r="D115" t="s">
-        <v>881</v>
+        <v>882</v>
       </c>
     </row>
     <row r="116" spans="4:4">
       <c r="D116" t="s">
-        <v>882</v>
+        <v>883</v>
       </c>
     </row>
     <row r="117" spans="3:3">
       <c r="C117" t="s">
-        <v>883</v>
+        <v>884</v>
       </c>
     </row>
     <row r="118" spans="4:4">
       <c r="D118" t="s">
-        <v>884</v>
+        <v>885</v>
       </c>
     </row>
     <row r="119" spans="4:4">
       <c r="D119" t="s">
-        <v>885</v>
+        <v>886</v>
       </c>
     </row>
     <row r="120" spans="4:4">
       <c r="D120" t="s">
-        <v>886</v>
+        <v>887</v>
       </c>
     </row>
     <row r="121" spans="3:3">
       <c r="C121" t="s">
-        <v>887</v>
+        <v>888</v>
       </c>
     </row>
     <row r="122" spans="2:2">
       <c r="B122" t="s">
-        <v>888</v>
+        <v>889</v>
       </c>
     </row>
     <row r="123" spans="3:3">
       <c r="C123" t="s">
-        <v>889</v>
+        <v>890</v>
       </c>
     </row>
     <row r="124" spans="4:4">
       <c r="D124" t="s">
-        <v>890</v>
+        <v>891</v>
       </c>
     </row>
     <row r="125" spans="4:4">
       <c r="D125" t="s">
-        <v>891</v>
+        <v>892</v>
       </c>
     </row>
     <row r="126" spans="4:4">
       <c r="D126" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
     </row>
     <row r="127" spans="3:3">
       <c r="C127" t="s">
-        <v>893</v>
+        <v>894</v>
       </c>
     </row>
     <row r="128" spans="4:4">
       <c r="D128" t="s">
-        <v>894</v>
+        <v>895</v>
       </c>
     </row>
     <row r="129" spans="4:4">
       <c r="D129" t="s">
-        <v>895</v>
+        <v>896</v>
       </c>
     </row>
     <row r="130" spans="4:4">
       <c r="D130" t="s">
-        <v>896</v>
+        <v>897</v>
       </c>
     </row>
     <row r="131" spans="4:4">
       <c r="D131" t="s">
-        <v>897</v>
+        <v>898</v>
       </c>
     </row>
     <row r="132" spans="4:4">
       <c r="D132" t="s">
-        <v>898</v>
+        <v>899</v>
       </c>
     </row>
     <row r="133" spans="4:4">
       <c r="D133" t="s">
-        <v>899</v>
+        <v>900</v>
       </c>
     </row>
     <row r="134" spans="4:4">
       <c r="D134" t="s">
-        <v>900</v>
+        <v>901</v>
       </c>
     </row>
     <row r="135" spans="3:3">
       <c r="C135" t="s">
-        <v>901</v>
+        <v>902</v>
       </c>
     </row>
     <row r="136" spans="3:3">
       <c r="C136" t="s">
-        <v>902</v>
+        <v>903</v>
       </c>
     </row>
     <row r="137" spans="4:4">
       <c r="D137" t="s">
-        <v>903</v>
+        <v>904</v>
       </c>
     </row>
     <row r="138" spans="4:4">
       <c r="D138" t="s">
-        <v>904</v>
+        <v>905</v>
       </c>
     </row>
     <row r="139" spans="4:4">
       <c r="D139" t="s">
-        <v>905</v>
+        <v>906</v>
       </c>
     </row>
     <row r="140" spans="4:4">
       <c r="D140" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
     </row>
     <row r="141" spans="4:4">
       <c r="D141" t="s">
-        <v>907</v>
+        <v>908</v>
       </c>
     </row>
     <row r="142" spans="2:2">
       <c r="B142" t="s">
-        <v>908</v>
+        <v>909</v>
       </c>
     </row>
     <row r="143" spans="3:3">
       <c r="C143" t="s">
-        <v>909</v>
+        <v>910</v>
       </c>
     </row>
     <row r="144" spans="2:2">
       <c r="B144" t="s">
-        <v>910</v>
+        <v>911</v>
       </c>
     </row>
     <row r="145" spans="3:3">
       <c r="C145" t="s">
-        <v>911</v>
+        <v>912</v>
       </c>
     </row>
     <row r="146" spans="2:2">
       <c r="B146" t="s">
-        <v>912</v>
+        <v>913</v>
       </c>
     </row>
     <row r="147" spans="3:3">
       <c r="C147" t="s">
-        <v>913</v>
+        <v>914</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:H8"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelRow="7" outlineLevelCol="7"/>
+  <cols>
+    <col min="1" max="1" width="9.66666666666667"/>
+  </cols>
+  <sheetData>
+    <row r="1" s="1" customFormat="1" spans="1:8">
+      <c r="A1" s="1">
+        <f>SUM(B1:AZ1)</f>
+        <v>2.5</v>
+      </c>
+      <c r="B1" s="1">
+        <f t="shared" ref="B1:H1" si="0">COUNTA(B2:B2058)/COLUMN()</f>
+        <v>1</v>
+      </c>
+      <c r="C1" s="1">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="D1" s="1">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+      <c r="E1" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F1" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G1" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H1" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2">
+        <v>20240427</v>
+      </c>
+      <c r="B2" t="s">
+        <v>915</v>
+      </c>
+    </row>
+    <row r="3" spans="3:3">
+      <c r="C3" t="s">
+        <v>916</v>
+      </c>
+    </row>
+    <row r="4" spans="2:2">
+      <c r="B4" t="s">
+        <v>917</v>
+      </c>
+    </row>
+    <row r="5" spans="3:3">
+      <c r="C5" t="s">
+        <v>918</v>
+      </c>
+    </row>
+    <row r="6" spans="3:3">
+      <c r="C6" t="s">
+        <v>919</v>
+      </c>
+    </row>
+    <row r="7" spans="4:4">
+      <c r="D7" t="s">
+        <v>920</v>
+      </c>
+    </row>
+    <row r="8" spans="4:4">
+      <c r="D8" t="s">
+        <v>921</v>
       </c>
     </row>
   </sheetData>
@@ -9958,28 +10078,28 @@
         <v>20240308</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="C2" s="3"/>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="3"/>
       <c r="B3" s="3" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="C3" s="3"/>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="3"/>
       <c r="B4" s="3" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="C4" s="3"/>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="3"/>
       <c r="B5" s="3" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="C5" s="3"/>
     </row>
@@ -9987,14 +10107,14 @@
       <c r="A6" s="3"/>
       <c r="B6" s="3"/>
       <c r="C6" s="3" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="3"/>
       <c r="B7" s="3"/>
       <c r="C7" s="3" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
     </row>
     <row r="8" spans="1:1">
@@ -10054,102 +10174,102 @@
         <v>20240309</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
     </row>
     <row r="3" spans="2:2">
       <c r="B3" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
     </row>
     <row r="4" spans="2:2">
       <c r="B4" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
     </row>
     <row r="5" spans="3:3">
       <c r="C5" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
     </row>
     <row r="6" spans="3:3">
       <c r="C6" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
     </row>
     <row r="7" spans="3:3">
       <c r="C7" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
     </row>
     <row r="8" spans="3:3">
       <c r="C8" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
     </row>
     <row r="9" spans="2:2">
       <c r="B9" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
     </row>
     <row r="10" spans="2:2">
       <c r="B10" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
     </row>
     <row r="11" spans="3:3">
       <c r="C11" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
     </row>
     <row r="12" spans="3:3">
       <c r="C12" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
     </row>
     <row r="13" spans="2:2">
       <c r="B13" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
     </row>
     <row r="14" spans="3:3">
       <c r="C14" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
     </row>
     <row r="15" spans="3:3">
       <c r="C15" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
     </row>
     <row r="16" spans="3:3">
       <c r="C16" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
     </row>
     <row r="17" spans="3:3">
       <c r="C17" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
     </row>
     <row r="18" spans="2:2">
       <c r="B18" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
     </row>
     <row r="19" spans="3:3">
       <c r="C19" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
     </row>
     <row r="20" spans="2:2">
       <c r="B20" s="6" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
     </row>
     <row r="21" spans="2:2">
       <c r="B21" s="6" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
     </row>
   </sheetData>
@@ -10206,47 +10326,47 @@
         <v>20240310</v>
       </c>
       <c r="B2" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
     </row>
     <row r="3" spans="3:3">
       <c r="C3" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
     </row>
     <row r="4" spans="2:2">
       <c r="B4" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
     </row>
     <row r="5" spans="3:3">
       <c r="C5" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
     </row>
     <row r="6" spans="2:2">
       <c r="B6" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
     </row>
     <row r="7" spans="3:3">
       <c r="C7" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
     </row>
     <row r="8" spans="4:4">
       <c r="D8" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
     </row>
     <row r="9" spans="3:3">
       <c r="C9" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="10" spans="4:4">
       <c r="D10" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
     </row>
   </sheetData>
@@ -10303,27 +10423,27 @@
         <v>20240311</v>
       </c>
       <c r="B2" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
     </row>
     <row r="3" spans="2:2">
       <c r="B3" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
     </row>
     <row r="4" spans="2:2">
       <c r="B4" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
     </row>
     <row r="5" spans="2:2">
       <c r="B5" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
     </row>
     <row r="6" spans="2:2">
       <c r="B6" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
     </row>
   </sheetData>
@@ -10377,42 +10497,42 @@
         <v>20240316</v>
       </c>
       <c r="B2" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
     </row>
     <row r="3" spans="2:2">
       <c r="B3" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
     </row>
     <row r="4" spans="3:3">
       <c r="C4" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
     </row>
     <row r="5" spans="3:3">
       <c r="C5" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
     </row>
     <row r="6" spans="3:3">
       <c r="C6" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
     </row>
     <row r="7" spans="2:2">
       <c r="B7" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
     </row>
     <row r="8" spans="2:2">
       <c r="B8" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
     </row>
     <row r="9" spans="2:2">
       <c r="B9" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
     </row>
     <row r="10" spans="2:2">
@@ -10469,102 +10589,102 @@
         <v>20240317</v>
       </c>
       <c r="B2" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
     </row>
     <row r="3" spans="3:3">
       <c r="C3" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
     </row>
     <row r="4" spans="4:4">
       <c r="D4" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
     </row>
     <row r="5" spans="4:4">
       <c r="D5" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
     </row>
     <row r="6" spans="5:5">
       <c r="E6" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
     </row>
     <row r="7" spans="5:5">
       <c r="E7" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
     </row>
     <row r="8" spans="6:6">
       <c r="F8" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
     </row>
     <row r="9" spans="5:5">
       <c r="E9" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
     </row>
     <row r="10" spans="6:6">
       <c r="F10" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
     </row>
     <row r="11" spans="3:3">
       <c r="C11" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
     </row>
     <row r="12" spans="4:4">
       <c r="D12" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
     </row>
     <row r="13" spans="4:4">
       <c r="D13" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
     </row>
     <row r="14" spans="4:4">
       <c r="D14" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
     </row>
     <row r="15" spans="5:5">
       <c r="E15" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
     </row>
     <row r="16" spans="4:4">
       <c r="D16" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
     </row>
     <row r="17" spans="5:5">
       <c r="E17" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
     </row>
     <row r="18" spans="5:5">
       <c r="E18" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
     </row>
     <row r="19" spans="6:6">
       <c r="F19" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
     </row>
     <row r="20" spans="5:5">
       <c r="E20" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
     </row>
     <row r="21" spans="6:6">
       <c r="F21" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
     </row>
   </sheetData>
